--- a/Aeolus-Wireframe-06.xlsx
+++ b/Aeolus-Wireframe-06.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aeolus\web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cld\Aeolus-Tire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53BF158-B33D-46BC-8F24-48C744D0BBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECC380A-6CB4-4314-A311-14226883891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18936" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30720" yWindow="552" windowWidth="23040" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Support" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4452" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="664">
   <si>
     <t>Tire Name</t>
   </si>
@@ -857,9 +857,6 @@
     <t>Steer axle tire for regional applications</t>
   </si>
   <si>
-    <t>Designed for use on “Last mile” delivery vehicles</t>
-  </si>
-  <si>
     <t>Excellent value and fully retreadable casing lowers operating costs</t>
   </si>
   <si>
@@ -918,9 +915,6 @@
   </si>
   <si>
     <t>Drive tire for highway, regional, urban use with 3PMS for winter traction on last-mile vehicles.</t>
-  </si>
-  <si>
-    <t>M+S, 3PMSF, Delivery Vehicles</t>
   </si>
   <si>
     <t>ADR55</t>
@@ -1077,9 +1071,6 @@
   </si>
   <si>
     <t>Drive tire for winter and urban last-mile use with 3PMS, low-temperature compound, excellent traction.</t>
-  </si>
-  <si>
-    <t>M+S, 3PMSF, Traction, Delivery Vehicles</t>
   </si>
   <si>
     <t>Tires Organized by Segment: (this will be the "Tires" drop down on the main website navBar)</t>
@@ -1299,9 +1290,6 @@
   </si>
   <si>
     <t>Truck tire with self-cleaning pattern, deep grooves, heavy-load capability, uniform wear, long-lasting.</t>
-  </si>
-  <si>
-    <t>Self Cleaning, Heavy Load, Long LifevM+S, 3PMSF</t>
   </si>
   <si>
     <t>Drive tire for On/ Off road applications</t>
@@ -1718,9 +1706,6 @@
     <t>Deep tread provides long mileage, reducing operating cost</t>
   </si>
   <si>
-    <t>Drive axle tire for smaller delivery vehicles in regional applications</t>
-  </si>
-  <si>
     <t>Drive axle tire for regional applications</t>
   </si>
   <si>
@@ -2021,10 +2006,43 @@
     <t>Neo-Allroads-D3-f2</t>
   </si>
   <si>
-    <t>Neo-Allroads-D3-f3</t>
+    <t>Removed:</t>
   </si>
   <si>
-    <t>Removed:</t>
+    <t>Uniform Block Pattern with Deeper Grooves</t>
+  </si>
+  <si>
+    <t>The consistent block layout and deeper tread grooves provide higher mileage while minimizing the risk of irregular wear, ensuring long-term performance and durability.</t>
+  </si>
+  <si>
+    <t>Four Longitudinal Grooves with Deepened 3D Steel Sipes</t>
+  </si>
+  <si>
+    <t>A 4-groove design integrated with deepened 3D steel sipes enhances traction and improves control on wet, snowy, and slippery roads for confident all-season driving.</t>
+  </si>
+  <si>
+    <t>The new dual-layer tread structure uses a medium- and long-distance compound formulation to balance mileage and heat dissipation, maintaining durability and performance even under heavy-duty operations.</t>
+  </si>
+  <si>
+    <t>ai rec' 12.2</t>
+  </si>
+  <si>
+    <t>ai rec' 11.6</t>
+  </si>
+  <si>
+    <t>ai rec' 11.7</t>
+  </si>
+  <si>
+    <t>Designed for use on “Last mile” Delivery Vehicle</t>
+  </si>
+  <si>
+    <t>M+S, 3PMSF, Delivery Vehicle</t>
+  </si>
+  <si>
+    <t>Drive axle tire for smaller Delivery Vehicle in regional applications</t>
+  </si>
+  <si>
+    <t>M+S, 3PMSF, Traction, Delivery Vehicle</t>
   </si>
 </sst>
 </file>
@@ -2222,7 +2240,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2292,6 +2310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2379,7 +2403,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -2788,7 +2812,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2816,6 +2839,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3147,35 +3177,35 @@
   <sheetData>
     <row r="1" spans="2:10" s="77" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="77" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C3" s="1">
         <v>8</v>
       </c>
       <c r="D3" s="81"/>
       <c r="E3" s="7" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F3" s="86"/>
       <c r="G3" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C4" s="1">
         <v>8</v>
@@ -3187,38 +3217,38 @@
         <v>244</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C5" s="1">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C6" s="1">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>252</v>
       </c>
       <c r="J6" s="95" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -3229,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
@@ -3244,10 +3274,10 @@
       </c>
       <c r="F8" s="85"/>
       <c r="G8" s="7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
@@ -3278,7 +3308,7 @@
         <v>268</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
@@ -3292,7 +3322,7 @@
         <v>102</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
@@ -3303,7 +3333,7 @@
         <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
@@ -3315,11 +3345,11 @@
       </c>
       <c r="D13" s="90"/>
       <c r="E13" s="7" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
@@ -3333,10 +3363,10 @@
         <v>115</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
@@ -3350,16 +3380,16 @@
         <v>149</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C16" s="1">
         <v>14</v>
@@ -3368,16 +3398,16 @@
         <v>161</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I16" s="96"/>
       <c r="J16" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C17" s="1">
         <v>15</v>
@@ -3386,12 +3416,12 @@
         <v>175</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C18" s="1">
         <v>15</v>
@@ -3400,18 +3430,18 @@
         <v>187</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C19" s="1">
         <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
@@ -3422,11 +3452,11 @@
         <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F20" s="82"/>
       <c r="G20" s="7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
@@ -3437,10 +3467,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
@@ -3451,7 +3481,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
@@ -3463,11 +3493,11 @@
       </c>
       <c r="D23" s="82"/>
       <c r="E23" s="7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -3478,15 +3508,15 @@
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C25" s="1">
         <v>20</v>
@@ -3495,7 +3525,7 @@
         <v>204</v>
       </c>
       <c r="G25" s="95" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
@@ -3506,7 +3536,7 @@
         <v>21</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
@@ -3518,11 +3548,11 @@
       </c>
       <c r="D27" s="83"/>
       <c r="E27" s="7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
@@ -3538,7 +3568,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="1">
         <v>23</v>
@@ -3548,53 +3578,53 @@
       </c>
       <c r="F29" s="83"/>
       <c r="G29" s="7" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C30" s="1">
         <v>23</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" s="1">
         <v>24</v>
       </c>
       <c r="D31" s="84"/>
       <c r="E31" s="7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32" s="1">
         <v>24</v>
       </c>
       <c r="E32" s="95" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C33" s="1">
         <v>25</v>
@@ -3605,7 +3635,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C34" s="1">
         <v>26</v>
@@ -3613,7 +3643,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C35" s="1">
         <v>26</v>
@@ -3621,7 +3651,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C36" s="1">
         <v>27</v>
@@ -3629,7 +3659,7 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C37" s="1">
         <v>28</v>
@@ -3637,138 +3667,138 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C38" s="1">
         <v>28</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C39" s="1">
         <v>29</v>
       </c>
       <c r="D39" s="81"/>
       <c r="E39" s="7" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C40" s="1">
         <v>29</v>
       </c>
       <c r="D40" s="90"/>
       <c r="E40" s="7" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C41" s="1">
         <v>30</v>
       </c>
       <c r="D41" s="82"/>
       <c r="E41" s="7" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C42" s="1">
         <v>30</v>
       </c>
       <c r="D42" s="83"/>
       <c r="E42" s="7" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C43" s="1">
         <v>32</v>
       </c>
       <c r="D43" s="84"/>
       <c r="E43" s="7" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C44" s="1">
         <v>32</v>
       </c>
       <c r="D44" s="86"/>
       <c r="E44" s="7" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C45" s="1">
         <v>33</v>
       </c>
       <c r="D45" s="85"/>
       <c r="E45" s="7" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D46" s="82"/>
       <c r="E46" s="7" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D47" s="83"/>
       <c r="E47" s="7" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -3776,7 +3806,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
@@ -3784,7 +3814,7 @@
         <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -3792,7 +3822,7 @@
         <v>89</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
@@ -3800,7 +3830,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -3808,7 +3838,7 @@
         <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
@@ -3816,7 +3846,7 @@
         <v>149</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
@@ -3824,7 +3854,7 @@
         <v>161</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
@@ -3832,7 +3862,7 @@
         <v>175</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -3840,15 +3870,15 @@
         <v>187</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -3856,7 +3886,7 @@
         <v>204</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -3864,7 +3894,7 @@
         <v>221</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
@@ -3872,11 +3902,12 @@
         <v>232</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3931,26 +3962,26 @@
       <c r="G1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="155" t="s">
+      <c r="H1" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="156"/>
-      <c r="J1" s="153" t="s">
+      <c r="I1" s="155"/>
+      <c r="J1" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="154"/>
-      <c r="L1" s="155" t="s">
+      <c r="K1" s="153"/>
+      <c r="L1" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="155" t="s">
+      <c r="M1" s="155"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
+      <c r="P1" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="155"/>
+      <c r="S1" s="155"/>
       <c r="T1" s="92" t="s">
         <v>10</v>
       </c>
@@ -3964,10 +3995,10 @@
         <v>13</v>
       </c>
       <c r="X1" s="43" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Z1" s="142" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -4027,7 +4058,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B3" s="97" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C3" s="138">
         <v>87010171</v>
@@ -4081,7 +4112,7 @@
         <v>830</v>
       </c>
       <c r="T3" s="98" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="U3" s="103"/>
       <c r="V3" s="103" t="s">
@@ -4091,7 +4122,7 @@
         <v>23</v>
       </c>
       <c r="X3" s="104" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
@@ -4148,7 +4179,7 @@
         <v>900</v>
       </c>
       <c r="T4" s="98" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="U4" s="103"/>
       <c r="V4" s="103" t="s">
@@ -4158,12 +4189,12 @@
         <v>23</v>
       </c>
       <c r="X4" s="104" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B5" s="97" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C5" s="138">
         <v>87010289</v>
@@ -4227,7 +4258,7 @@
         <v>23</v>
       </c>
       <c r="X5" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AA5" s="1"/>
     </row>
@@ -4293,7 +4324,7 @@
       </c>
       <c r="W6" s="103"/>
       <c r="X6" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
@@ -4302,7 +4333,7 @@
         <v>87010243</v>
       </c>
       <c r="D7" s="98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E7" s="98">
         <v>20</v>
@@ -4350,7 +4381,7 @@
         <v>900</v>
       </c>
       <c r="T7" s="98" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="U7" s="103"/>
       <c r="V7" s="103" t="s">
@@ -4360,7 +4391,7 @@
         <v>23</v>
       </c>
       <c r="X7" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z7" s="74"/>
       <c r="AA7" s="1"/>
@@ -4430,7 +4461,7 @@
         <v>23</v>
       </c>
       <c r="X8" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z8" s="74"/>
       <c r="AA8" s="1"/>
@@ -4490,7 +4521,7 @@
         <v>830</v>
       </c>
       <c r="T9" s="98" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="U9" s="103"/>
       <c r="V9" s="103" t="s">
@@ -4500,7 +4531,7 @@
         <v>23</v>
       </c>
       <c r="X9" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z9" s="74"/>
       <c r="AA9" s="1"/>
@@ -4560,7 +4591,7 @@
         <v>830</v>
       </c>
       <c r="T10" s="98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U10" s="103"/>
       <c r="V10" s="103" t="s">
@@ -4570,7 +4601,7 @@
         <v>23</v>
       </c>
       <c r="X10" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z10" s="74"/>
       <c r="AA10" s="1"/>
@@ -4630,7 +4661,7 @@
         <v>900</v>
       </c>
       <c r="T11" s="98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U11" s="103"/>
       <c r="V11" s="103" t="s">
@@ -4640,7 +4671,7 @@
         <v>23</v>
       </c>
       <c r="X11" s="104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z11" s="74"/>
       <c r="AA11" s="1"/>
@@ -4710,7 +4741,7 @@
       </c>
       <c r="W12" s="103"/>
       <c r="X12" s="104" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="Z12" s="74"/>
       <c r="AA12" s="1"/>
@@ -4778,7 +4809,7 @@
       </c>
       <c r="W13" s="103"/>
       <c r="X13" s="104" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="Z13" s="74"/>
       <c r="AA13" s="1"/>
@@ -4854,13 +4885,13 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="97" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15" s="138">
         <v>87030158</v>
       </c>
       <c r="D15" s="98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E15" s="98">
         <v>18</v>
@@ -4908,7 +4939,7 @@
         <v>930</v>
       </c>
       <c r="T15" s="98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U15" s="103"/>
       <c r="V15" s="103" t="s">
@@ -4916,7 +4947,7 @@
       </c>
       <c r="W15" s="103"/>
       <c r="X15" s="104" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Z15" s="74"/>
       <c r="AA15" s="1"/>
@@ -4924,7 +4955,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="97" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C16" s="138">
         <v>87030229</v>
@@ -4978,7 +5009,7 @@
         <v>830</v>
       </c>
       <c r="T16" s="98" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U16" s="103"/>
       <c r="V16" s="103" t="s">
@@ -4988,7 +5019,7 @@
         <v>23</v>
       </c>
       <c r="X16" s="104" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Z16" s="74"/>
       <c r="AA16" s="1"/>
@@ -5056,7 +5087,7 @@
       </c>
       <c r="W17" s="103"/>
       <c r="X17" s="104" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Z17" s="74"/>
       <c r="AA17" s="1"/>
@@ -5064,7 +5095,7 @@
     </row>
     <row r="18" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B18" s="97" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C18" s="140">
         <v>87030328</v>
@@ -5128,7 +5159,7 @@
         <v>23</v>
       </c>
       <c r="X18" s="104" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z18" s="74"/>
       <c r="AA18" s="1"/>
@@ -5198,7 +5229,7 @@
         <v>23</v>
       </c>
       <c r="X19" s="104" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z19" s="74"/>
       <c r="AA19" s="1"/>
@@ -5206,13 +5237,13 @@
     </row>
     <row r="20" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B20" s="97" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C20" s="138">
         <v>87030442</v>
       </c>
       <c r="D20" s="98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E20" s="98">
         <v>16</v>
@@ -5270,7 +5301,7 @@
         <v>23</v>
       </c>
       <c r="X20" s="104" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z20" s="74"/>
       <c r="AA20" s="1"/>
@@ -5340,7 +5371,7 @@
         <v>23</v>
       </c>
       <c r="X21" s="104" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z21" s="74"/>
       <c r="AA21" s="1"/>
@@ -5410,7 +5441,7 @@
         <v>23</v>
       </c>
       <c r="X22" s="104" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z22" s="74"/>
       <c r="AA22" s="1"/>
@@ -5418,7 +5449,7 @@
     </row>
     <row r="23" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B23" s="97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C23" s="138">
         <v>87030584</v>
@@ -5480,7 +5511,7 @@
       </c>
       <c r="W23" s="103"/>
       <c r="X23" s="104" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Z23" s="74"/>
       <c r="AA23" s="1"/>
@@ -5548,7 +5579,7 @@
       </c>
       <c r="W24" s="103"/>
       <c r="X24" s="104" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Z24" s="74"/>
       <c r="AA24" s="1"/>
@@ -5556,7 +5587,7 @@
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B25" s="97" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C25" s="138">
         <v>87030625</v>
@@ -5610,7 +5641,7 @@
         <v>900</v>
       </c>
       <c r="T25" s="98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U25" s="103"/>
       <c r="V25" s="103" t="s">
@@ -5620,7 +5651,7 @@
         <v>23</v>
       </c>
       <c r="X25" s="104" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Z25" s="74"/>
       <c r="AA25" s="1"/>
@@ -5768,7 +5799,7 @@
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B28" s="97" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C28" s="138">
         <v>87040143</v>
@@ -5822,7 +5853,7 @@
         <v>830</v>
       </c>
       <c r="T28" s="98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U28" s="103"/>
       <c r="V28" s="103" t="s">
@@ -5832,7 +5863,7 @@
         <v>23</v>
       </c>
       <c r="X28" s="104" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Z28" s="74"/>
       <c r="AA28" s="1"/>
@@ -5892,7 +5923,7 @@
         <v>900</v>
       </c>
       <c r="T29" s="98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U29" s="103"/>
       <c r="V29" s="103" t="s">
@@ -5902,7 +5933,7 @@
         <v>23</v>
       </c>
       <c r="X29" s="104" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Z29" s="74"/>
       <c r="AA29" s="1"/>
@@ -5910,7 +5941,7 @@
     </row>
     <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B30" s="97" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C30" s="138">
         <v>87040254</v>
@@ -5974,7 +6005,7 @@
         <v>23</v>
       </c>
       <c r="X30" s="104" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Z30" s="74"/>
       <c r="AA30" s="1"/>
@@ -6044,7 +6075,7 @@
         <v>23</v>
       </c>
       <c r="X31" s="104" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Z31" s="74"/>
       <c r="AA31" s="1"/>
@@ -6052,7 +6083,7 @@
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B32" s="97" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C32" s="138">
         <v>87040322</v>
@@ -6116,7 +6147,7 @@
         <v>23</v>
       </c>
       <c r="X32" s="104" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Z32" s="74"/>
       <c r="AA32" s="1"/>
@@ -6186,7 +6217,7 @@
         <v>23</v>
       </c>
       <c r="X33" s="104" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Z33" s="74"/>
       <c r="AA33" s="1"/>
@@ -6194,7 +6225,7 @@
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" s="97" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C34" s="138">
         <v>87110160</v>
@@ -6248,7 +6279,7 @@
         <v>830</v>
       </c>
       <c r="T34" s="98" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="U34" s="103"/>
       <c r="V34" s="103" t="s">
@@ -6258,7 +6289,7 @@
         <v>23</v>
       </c>
       <c r="X34" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z34" s="74"/>
       <c r="AA34" s="1"/>
@@ -6318,7 +6349,7 @@
         <v>930</v>
       </c>
       <c r="T35" s="98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U35" s="103"/>
       <c r="V35" s="103" t="s">
@@ -6328,7 +6359,7 @@
         <v>23</v>
       </c>
       <c r="X35" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z35" s="74"/>
       <c r="AA35" s="1"/>
@@ -6340,7 +6371,7 @@
         <v>87110184</v>
       </c>
       <c r="D36" s="98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E36" s="98">
         <v>18</v>
@@ -6388,7 +6419,7 @@
         <v>930</v>
       </c>
       <c r="T36" s="98" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="U36" s="103"/>
       <c r="V36" s="103" t="s">
@@ -6398,7 +6429,7 @@
         <v>23</v>
       </c>
       <c r="X36" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z36" s="74"/>
       <c r="AA36" s="1"/>
@@ -6410,7 +6441,7 @@
         <v>87110138</v>
       </c>
       <c r="D37" s="98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E37" s="98">
         <v>16</v>
@@ -6468,7 +6499,7 @@
         <v>23</v>
       </c>
       <c r="X37" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z37" s="74"/>
       <c r="AA37" s="1"/>
@@ -6538,7 +6569,7 @@
         <v>23</v>
       </c>
       <c r="X38" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z38" s="74"/>
       <c r="AA38" s="1"/>
@@ -6604,7 +6635,7 @@
       <c r="V39" s="120"/>
       <c r="W39" s="103"/>
       <c r="X39" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z39" s="74"/>
       <c r="AA39" s="1"/>
@@ -6616,7 +6647,7 @@
         <v>87110136</v>
       </c>
       <c r="D40" s="106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E40" s="106">
         <v>18</v>
@@ -6664,7 +6695,7 @@
         <v>830</v>
       </c>
       <c r="T40" s="106" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="U40" s="110"/>
       <c r="V40" s="141" t="s">
@@ -6672,7 +6703,7 @@
       </c>
       <c r="W40" s="110"/>
       <c r="X40" s="111" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z40" s="74"/>
       <c r="AA40" s="1"/>
@@ -6684,7 +6715,7 @@
         <v>87110195</v>
       </c>
       <c r="D41" s="98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E41" s="98">
         <v>20</v>
@@ -6732,7 +6763,7 @@
         <v>900</v>
       </c>
       <c r="T41" s="98" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="U41" s="103"/>
       <c r="V41" s="103" t="s">
@@ -6742,7 +6773,7 @@
         <v>23</v>
       </c>
       <c r="X41" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z41" s="74"/>
       <c r="AA41" s="1"/>
@@ -6812,7 +6843,7 @@
         <v>23</v>
       </c>
       <c r="X42" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z42" s="74"/>
       <c r="AA42" s="1"/>
@@ -6824,7 +6855,7 @@
         <v>87110168</v>
       </c>
       <c r="D43" s="98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E43" s="98">
         <v>18</v>
@@ -6872,13 +6903,13 @@
         <v>930</v>
       </c>
       <c r="T43" s="98" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="U43" s="103"/>
       <c r="V43" s="120"/>
       <c r="W43" s="103"/>
       <c r="X43" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z43" s="74"/>
       <c r="AA43" s="1"/>
@@ -6938,7 +6969,7 @@
         <v>900</v>
       </c>
       <c r="T44" s="98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U44" s="103"/>
       <c r="V44" s="103" t="s">
@@ -6948,7 +6979,7 @@
         <v>23</v>
       </c>
       <c r="X44" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z44" s="74"/>
       <c r="AA44" s="1"/>
@@ -7008,7 +7039,7 @@
         <v>900</v>
       </c>
       <c r="T45" s="98" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="U45" s="103"/>
       <c r="V45" s="103" t="s">
@@ -7016,7 +7047,7 @@
       </c>
       <c r="W45" s="103"/>
       <c r="X45" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z45" s="74"/>
       <c r="AA45" s="1"/>
@@ -7076,7 +7107,7 @@
         <v>900</v>
       </c>
       <c r="T46" s="98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="U46" s="103"/>
       <c r="V46" s="103" t="s">
@@ -7086,7 +7117,7 @@
         <v>23</v>
       </c>
       <c r="X46" s="104" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Z46" s="74"/>
       <c r="AA46" s="1"/>
@@ -7094,7 +7125,7 @@
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B47" s="97" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C47" s="138">
         <v>87110266</v>
@@ -7158,7 +7189,7 @@
         <v>23</v>
       </c>
       <c r="X47" s="104" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.3">
@@ -7225,7 +7256,7 @@
         <v>23</v>
       </c>
       <c r="X48" s="104" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.3">
@@ -7234,7 +7265,7 @@
         <v>87110227</v>
       </c>
       <c r="D49" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E49" s="106">
         <v>20</v>
@@ -7274,7 +7305,7 @@
       <c r="R49" s="106"/>
       <c r="S49" s="106"/>
       <c r="T49" s="106" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="U49" s="110"/>
       <c r="V49" s="110" t="s">
@@ -7282,7 +7313,7 @@
       </c>
       <c r="W49" s="110"/>
       <c r="X49" s="111" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.3">
@@ -7341,7 +7372,7 @@
         <v>23</v>
       </c>
       <c r="X50" s="104" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.3">
@@ -7400,7 +7431,7 @@
         <v>23</v>
       </c>
       <c r="X51" s="104" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.3">
@@ -7459,12 +7490,12 @@
         <v>23</v>
       </c>
       <c r="X52" s="104" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B53" s="97" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C53" s="138">
         <v>87120154</v>
@@ -7518,15 +7549,15 @@
         <v>930</v>
       </c>
       <c r="T53" s="98" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="U53" s="103"/>
       <c r="V53" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W53" s="103"/>
       <c r="X53" s="104" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.3">
@@ -7583,15 +7614,15 @@
         <v>830</v>
       </c>
       <c r="T54" s="98" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="U54" s="103"/>
       <c r="V54" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W54" s="103"/>
       <c r="X54" s="104" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.3">
@@ -7600,7 +7631,7 @@
         <v>87120113</v>
       </c>
       <c r="D55" s="98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E55" s="98">
         <v>20</v>
@@ -7648,15 +7679,15 @@
         <v>900</v>
       </c>
       <c r="T55" s="98" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="U55" s="103"/>
       <c r="V55" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W55" s="103"/>
       <c r="X55" s="104" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.3">
@@ -7713,20 +7744,20 @@
         <v>930</v>
       </c>
       <c r="T56" s="98" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="U56" s="103"/>
       <c r="V56" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W56" s="103"/>
       <c r="X56" s="104" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B57" s="97" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C57" s="138">
         <v>87120237</v>
@@ -7780,15 +7811,15 @@
         <v>830</v>
       </c>
       <c r="T57" s="98" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="U57" s="103"/>
       <c r="V57" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W57" s="103"/>
       <c r="X57" s="104" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.3">
@@ -7845,20 +7876,20 @@
         <v>830</v>
       </c>
       <c r="T58" s="98" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="U58" s="103"/>
       <c r="V58" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W58" s="103"/>
       <c r="X58" s="104" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B59" s="97" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C59" s="138">
         <v>87130136</v>
@@ -7918,7 +7949,7 @@
       <c r="V59" s="120"/>
       <c r="W59" s="103"/>
       <c r="X59" s="104" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.3">
@@ -7981,7 +8012,7 @@
       <c r="V60" s="120"/>
       <c r="W60" s="103"/>
       <c r="X60" s="104" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.3">
@@ -8038,18 +8069,18 @@
         <v>900</v>
       </c>
       <c r="T61" s="98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="U61" s="103"/>
       <c r="V61" s="120"/>
       <c r="W61" s="103"/>
       <c r="X61" s="104" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B62" s="97" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C62" s="138">
         <v>87210997</v>
@@ -8111,29 +8142,29 @@
       </c>
       <c r="W62" s="103"/>
       <c r="X62" s="104" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B63" s="148" t="s">
+      <c r="B63" s="147" t="s">
         <v>244</v>
       </c>
       <c r="C63" s="139">
         <v>87210146</v>
       </c>
-      <c r="D63" s="149" t="s">
+      <c r="D63" s="148" t="s">
         <v>57</v>
       </c>
-      <c r="E63" s="149">
+      <c r="E63" s="148">
         <v>16</v>
       </c>
-      <c r="F63" s="150">
+      <c r="F63" s="149">
         <v>8.25</v>
       </c>
-      <c r="G63" s="151">
+      <c r="G63" s="150">
         <v>10.9</v>
       </c>
-      <c r="H63" s="151">
+      <c r="H63" s="150">
         <v>41.4</v>
       </c>
       <c r="I63" s="129">
@@ -8142,7 +8173,7 @@
       <c r="J63" s="129">
         <v>15</v>
       </c>
-      <c r="K63" s="152">
+      <c r="K63" s="151">
         <v>19</v>
       </c>
       <c r="L63" s="129">
@@ -8163,13 +8194,13 @@
       <c r="Q63" s="129">
         <v>120</v>
       </c>
-      <c r="R63" s="149">
+      <c r="R63" s="148">
         <v>2725</v>
       </c>
-      <c r="S63" s="149">
+      <c r="S63" s="148">
         <v>830</v>
       </c>
-      <c r="T63" s="149" t="s">
+      <c r="T63" s="148" t="s">
         <v>56</v>
       </c>
       <c r="U63" s="141"/>
@@ -8181,7 +8212,7 @@
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B64" s="97" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C64" s="138">
         <v>87210391</v>
@@ -8245,7 +8276,7 @@
       </c>
       <c r="W64" s="103"/>
       <c r="X64" s="104" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.3">
@@ -8310,7 +8341,7 @@
       <c r="V65" s="120"/>
       <c r="W65" s="103"/>
       <c r="X65" s="104" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.3">
@@ -8375,7 +8406,7 @@
       <c r="V66" s="121"/>
       <c r="W66" s="110"/>
       <c r="X66" s="111" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.3">
@@ -8849,13 +8880,13 @@
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" s="97" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C74" s="138">
         <v>87220455</v>
       </c>
       <c r="D74" s="98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E74" s="98">
         <v>16</v>
@@ -8911,7 +8942,7 @@
       </c>
       <c r="W74" s="103"/>
       <c r="X74" s="104" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.3">
@@ -8976,12 +9007,12 @@
       </c>
       <c r="W75" s="103"/>
       <c r="X75" s="104" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B76" s="97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C76" s="138">
         <v>87220581</v>
@@ -9045,7 +9076,7 @@
         <v>23</v>
       </c>
       <c r="X76" s="104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.3">
@@ -9102,7 +9133,7 @@
         <v>900</v>
       </c>
       <c r="T77" s="98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U77" s="103"/>
       <c r="V77" s="103" t="s">
@@ -9112,18 +9143,18 @@
         <v>23</v>
       </c>
       <c r="X77" s="104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B78" s="97" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C78" s="138">
         <v>87220622</v>
       </c>
       <c r="D78" s="98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E78" s="98">
         <v>16</v>
@@ -9181,7 +9212,7 @@
         <v>23</v>
       </c>
       <c r="X78" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.3">
@@ -9248,7 +9279,7 @@
         <v>23</v>
       </c>
       <c r="X79" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.3">
@@ -9315,7 +9346,7 @@
         <v>23</v>
       </c>
       <c r="X80" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.3">
@@ -9382,7 +9413,7 @@
         <v>23</v>
       </c>
       <c r="X81" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.3">
@@ -9449,7 +9480,7 @@
         <v>23</v>
       </c>
       <c r="X82" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.3">
@@ -9516,7 +9547,7 @@
         <v>23</v>
       </c>
       <c r="X83" s="104" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.3">
@@ -9525,7 +9556,7 @@
         <v>87220693</v>
       </c>
       <c r="D84" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E84" s="106">
         <v>16</v>
@@ -9581,7 +9612,7 @@
       </c>
       <c r="W84" s="110"/>
       <c r="X84" s="111" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.3">
@@ -9651,13 +9682,13 @@
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B86" s="97" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C86" s="138">
         <v>87320125</v>
       </c>
       <c r="D86" s="98" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E86" s="98">
         <v>18</v>
@@ -9697,7 +9728,7 @@
       <c r="R86" s="123"/>
       <c r="S86" s="123"/>
       <c r="T86" s="98" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="U86" s="103"/>
       <c r="V86" s="103" t="s">
@@ -9707,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="X86" s="104" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.3">
@@ -9756,7 +9787,7 @@
       <c r="R87" s="123"/>
       <c r="S87" s="123"/>
       <c r="T87" s="98" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="U87" s="103"/>
       <c r="V87" s="103" t="s">
@@ -9766,7 +9797,7 @@
         <v>23</v>
       </c>
       <c r="X87" s="104" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.3">
@@ -9835,7 +9866,7 @@
         <v>23</v>
       </c>
       <c r="X88" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.3">
@@ -9902,7 +9933,7 @@
         <v>23</v>
       </c>
       <c r="X89" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.3">
@@ -9969,7 +10000,7 @@
         <v>23</v>
       </c>
       <c r="X90" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.3">
@@ -10036,7 +10067,7 @@
         <v>23</v>
       </c>
       <c r="X91" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.3">
@@ -10103,7 +10134,7 @@
         <v>23</v>
       </c>
       <c r="X92" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.3">
@@ -10170,7 +10201,7 @@
         <v>23</v>
       </c>
       <c r="X93" s="104" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="2:24" x14ac:dyDescent="0.3">
@@ -10179,7 +10210,7 @@
         <v>17410196</v>
       </c>
       <c r="D94" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E94" s="106">
         <v>16</v>
@@ -10227,7 +10258,7 @@
         <v>830</v>
       </c>
       <c r="T94" s="106" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="U94" s="110"/>
       <c r="V94" s="110" t="s">
@@ -10235,7 +10266,7 @@
       </c>
       <c r="W94" s="110"/>
       <c r="X94" s="111" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="2:24" x14ac:dyDescent="0.3">
@@ -10244,7 +10275,7 @@
         <v>17410148</v>
       </c>
       <c r="D95" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E95" s="106">
         <v>18</v>
@@ -10300,7 +10331,7 @@
       </c>
       <c r="W95" s="110"/>
       <c r="X95" s="111" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="96" spans="2:24" x14ac:dyDescent="0.3">
@@ -10369,7 +10400,7 @@
         <v>23</v>
       </c>
       <c r="X96" s="104" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="97" spans="2:24" x14ac:dyDescent="0.3">
@@ -10436,7 +10467,7 @@
         <v>23</v>
       </c>
       <c r="X97" s="104" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="2:24" x14ac:dyDescent="0.3">
@@ -10503,12 +10534,12 @@
         <v>23</v>
       </c>
       <c r="X98" s="104" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="99" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B99" s="97" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C99" s="138">
         <v>17410770</v>
@@ -10570,7 +10601,7 @@
       </c>
       <c r="W99" s="103"/>
       <c r="X99" s="104" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="100" spans="2:24" x14ac:dyDescent="0.3">
@@ -10627,7 +10658,7 @@
         <v>830</v>
       </c>
       <c r="T100" s="106" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="U100" s="110"/>
       <c r="V100" s="110" t="s">
@@ -10635,7 +10666,7 @@
       </c>
       <c r="W100" s="110"/>
       <c r="X100" s="111" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="101" spans="2:24" x14ac:dyDescent="0.3">
@@ -10702,7 +10733,7 @@
       </c>
       <c r="W101" s="118"/>
       <c r="X101" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" spans="2:24" x14ac:dyDescent="0.3">
@@ -10769,7 +10800,7 @@
         <v>23</v>
       </c>
       <c r="X102" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="103" spans="2:24" x14ac:dyDescent="0.3">
@@ -10836,7 +10867,7 @@
         <v>23</v>
       </c>
       <c r="X103" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="104" spans="2:24" x14ac:dyDescent="0.3">
@@ -10903,7 +10934,7 @@
         <v>23</v>
       </c>
       <c r="X104" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="105" spans="2:24" x14ac:dyDescent="0.3">
@@ -10970,7 +11001,7 @@
         <v>23</v>
       </c>
       <c r="X105" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="2:24" x14ac:dyDescent="0.3">
@@ -11037,7 +11068,7 @@
         <v>23</v>
       </c>
       <c r="X106" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="2:24" x14ac:dyDescent="0.3">
@@ -11102,7 +11133,7 @@
       </c>
       <c r="W107" s="103"/>
       <c r="X107" s="104" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="2:24" x14ac:dyDescent="0.3">
@@ -11163,7 +11194,7 @@
         <v>23</v>
       </c>
       <c r="X108" s="104" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="2:24" x14ac:dyDescent="0.3">
@@ -11172,7 +11203,7 @@
         <v>17410490</v>
       </c>
       <c r="D109" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E109" s="106">
         <v>20</v>
@@ -11212,7 +11243,7 @@
       <c r="R109" s="106"/>
       <c r="S109" s="106"/>
       <c r="T109" s="106" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="U109" s="110"/>
       <c r="V109" s="110" t="s">
@@ -11220,7 +11251,7 @@
       </c>
       <c r="W109" s="110"/>
       <c r="X109" s="111" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="110" spans="2:24" x14ac:dyDescent="0.3">
@@ -11289,7 +11320,7 @@
         <v>23</v>
       </c>
       <c r="X110" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="2:24" x14ac:dyDescent="0.3">
@@ -11356,7 +11387,7 @@
         <v>23</v>
       </c>
       <c r="X111" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="2:24" x14ac:dyDescent="0.3">
@@ -11423,7 +11454,7 @@
         <v>23</v>
       </c>
       <c r="X112" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="2:24" x14ac:dyDescent="0.3">
@@ -11432,7 +11463,7 @@
         <v>17410586</v>
       </c>
       <c r="D113" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E113" s="106">
         <v>18</v>
@@ -11488,7 +11519,7 @@
       </c>
       <c r="W113" s="110"/>
       <c r="X113" s="111" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="2:24" x14ac:dyDescent="0.3">
@@ -11555,7 +11586,7 @@
         <v>23</v>
       </c>
       <c r="X114" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="2:24" x14ac:dyDescent="0.3">
@@ -11564,7 +11595,7 @@
         <v>17410593</v>
       </c>
       <c r="D115" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E115" s="106">
         <v>24</v>
@@ -11612,7 +11643,7 @@
       </c>
       <c r="W115" s="110"/>
       <c r="X115" s="111" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="2:24" x14ac:dyDescent="0.3">
@@ -11669,7 +11700,7 @@
       </c>
       <c r="W116" s="110"/>
       <c r="X116" s="111" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="2:24" x14ac:dyDescent="0.3">
@@ -11728,7 +11759,7 @@
         <v>23</v>
       </c>
       <c r="X117" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="2:24" x14ac:dyDescent="0.3">
@@ -11787,12 +11818,12 @@
         <v>23</v>
       </c>
       <c r="X118" s="104" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="119" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B119" s="97" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C119" s="138">
         <v>17410689</v>
@@ -11846,7 +11877,7 @@
         <v>830</v>
       </c>
       <c r="T119" s="113" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="U119" s="103"/>
       <c r="V119" s="103" t="s">
@@ -11854,7 +11885,7 @@
       </c>
       <c r="W119" s="103"/>
       <c r="X119" s="104" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="120" spans="2:24" x14ac:dyDescent="0.3">
@@ -11923,7 +11954,7 @@
         <v>23</v>
       </c>
       <c r="X120" s="104" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="121" spans="2:24" x14ac:dyDescent="0.3">
@@ -11990,12 +12021,12 @@
         <v>23</v>
       </c>
       <c r="X121" s="104" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B122" s="97" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C122" s="138">
         <v>17420178</v>
@@ -12057,7 +12088,7 @@
       </c>
       <c r="W122" s="103"/>
       <c r="X122" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="2:24" x14ac:dyDescent="0.3">
@@ -12122,7 +12153,7 @@
       </c>
       <c r="W123" s="103"/>
       <c r="X123" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="2:24" x14ac:dyDescent="0.3">
@@ -12187,7 +12218,7 @@
       </c>
       <c r="W124" s="103"/>
       <c r="X124" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="2:24" x14ac:dyDescent="0.3">
@@ -12254,7 +12285,7 @@
         <v>23</v>
       </c>
       <c r="X125" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="2:24" x14ac:dyDescent="0.3">
@@ -12321,7 +12352,7 @@
         <v>23</v>
       </c>
       <c r="X126" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="2:24" x14ac:dyDescent="0.3">
@@ -12380,7 +12411,7 @@
         <v>23</v>
       </c>
       <c r="X127" s="104" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="2:24" x14ac:dyDescent="0.3">
@@ -12437,7 +12468,7 @@
         <v>900</v>
       </c>
       <c r="T128" s="130" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="U128" s="110"/>
       <c r="V128" s="110" t="s">
@@ -12445,7 +12476,7 @@
       </c>
       <c r="W128" s="110"/>
       <c r="X128" s="111" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="2:24" x14ac:dyDescent="0.3">
@@ -12454,7 +12485,7 @@
         <v>17430150</v>
       </c>
       <c r="D129" s="106" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E129" s="106">
         <v>22</v>
@@ -12502,7 +12533,7 @@
         <v>850</v>
       </c>
       <c r="T129" s="130" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="U129" s="110"/>
       <c r="V129" s="110" t="s">
@@ -12510,7 +12541,7 @@
       </c>
       <c r="W129" s="110"/>
       <c r="X129" s="111" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="2:24" x14ac:dyDescent="0.3">
@@ -12577,7 +12608,7 @@
       </c>
       <c r="W130" s="103"/>
       <c r="X130" s="104" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="2:24" x14ac:dyDescent="0.3">
@@ -12642,7 +12673,7 @@
       </c>
       <c r="W131" s="103"/>
       <c r="X131" s="104" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="2:24" x14ac:dyDescent="0.3">
@@ -12709,7 +12740,7 @@
         <v>23</v>
       </c>
       <c r="X132" s="104" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="2:24" x14ac:dyDescent="0.3">
@@ -12776,7 +12807,7 @@
         <v>23</v>
       </c>
       <c r="X133" s="104" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="2:24" x14ac:dyDescent="0.3">
@@ -12833,7 +12864,7 @@
         <v>900</v>
       </c>
       <c r="T134" s="130" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="U134" s="110"/>
       <c r="V134" s="110" t="s">
@@ -12841,7 +12872,7 @@
       </c>
       <c r="W134" s="110"/>
       <c r="X134" s="111" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="2:24" x14ac:dyDescent="0.3">
@@ -12850,7 +12881,7 @@
         <v>17430247</v>
       </c>
       <c r="D135" s="106" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E135" s="106">
         <v>22</v>
@@ -12898,7 +12929,7 @@
         <v>850</v>
       </c>
       <c r="T135" s="130" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="U135" s="110"/>
       <c r="V135" s="110" t="s">
@@ -12906,7 +12937,7 @@
       </c>
       <c r="W135" s="110"/>
       <c r="X135" s="111" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="2:24" x14ac:dyDescent="0.3">
@@ -12965,12 +12996,12 @@
         <v>23</v>
       </c>
       <c r="X136" s="104" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B137" s="105" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C137" s="139">
         <v>17440150</v>
@@ -13032,7 +13063,7 @@
       </c>
       <c r="W137" s="110"/>
       <c r="X137" s="111" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="138" spans="2:24" x14ac:dyDescent="0.3">
@@ -13101,7 +13132,7 @@
         <v>23</v>
       </c>
       <c r="X138" s="104" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="2:24" x14ac:dyDescent="0.3">
@@ -13158,7 +13189,7 @@
       </c>
       <c r="W139" s="103"/>
       <c r="X139" s="104" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="2:24" x14ac:dyDescent="0.3">
@@ -13225,7 +13256,7 @@
       </c>
       <c r="W140" s="103"/>
       <c r="X140" s="104" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="2:24" x14ac:dyDescent="0.3">
@@ -13292,7 +13323,7 @@
       </c>
       <c r="W141" s="103"/>
       <c r="X141" s="104" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="2:24" x14ac:dyDescent="0.3">
@@ -13359,7 +13390,7 @@
       </c>
       <c r="W142" s="103"/>
       <c r="X142" s="104" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="2:24" x14ac:dyDescent="0.3">
@@ -13426,7 +13457,7 @@
       </c>
       <c r="W143" s="103"/>
       <c r="X143" s="104" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="2:24" x14ac:dyDescent="0.3">
@@ -13493,7 +13524,7 @@
       </c>
       <c r="W144" s="103"/>
       <c r="X144" s="104" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" spans="2:24" x14ac:dyDescent="0.3">
@@ -13560,7 +13591,7 @@
       </c>
       <c r="W145" s="103"/>
       <c r="X145" s="104" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146" spans="2:24" x14ac:dyDescent="0.3">
@@ -13629,7 +13660,7 @@
         <v>23</v>
       </c>
       <c r="X146" s="104" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="147" spans="2:24" x14ac:dyDescent="0.3">
@@ -13696,7 +13727,7 @@
         <v>23</v>
       </c>
       <c r="X147" s="104" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="148" spans="2:24" x14ac:dyDescent="0.3">
@@ -13755,7 +13786,7 @@
       </c>
       <c r="W148" s="103"/>
       <c r="X148" s="104" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="2:24" x14ac:dyDescent="0.3">
@@ -13814,7 +13845,7 @@
       </c>
       <c r="W149" s="103"/>
       <c r="X149" s="104" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="2:24" x14ac:dyDescent="0.3">
@@ -13873,7 +13904,7 @@
         <v>830</v>
       </c>
       <c r="T150" s="113" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="U150" s="133"/>
       <c r="V150" s="103" t="s">
@@ -13881,7 +13912,7 @@
       </c>
       <c r="W150" s="103"/>
       <c r="X150" s="104" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="2:24" x14ac:dyDescent="0.3">
@@ -13944,12 +13975,12 @@
       <c r="V151" s="134"/>
       <c r="W151" s="110"/>
       <c r="X151" s="111" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="152" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B152" s="97" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C152" s="138">
         <v>17470183</v>
@@ -14003,7 +14034,7 @@
         <v>850</v>
       </c>
       <c r="T152" s="113" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="U152" s="103"/>
       <c r="V152" s="103" t="s">
@@ -14013,7 +14044,7 @@
         <v>23</v>
       </c>
       <c r="X152" s="104" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="2:24" x14ac:dyDescent="0.3">
@@ -14080,7 +14111,7 @@
         <v>23</v>
       </c>
       <c r="X153" s="104" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="2:24" x14ac:dyDescent="0.3">
@@ -14149,7 +14180,7 @@
         <v>23</v>
       </c>
       <c r="X154" s="104" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="2:24" x14ac:dyDescent="0.3">
@@ -14216,12 +14247,12 @@
         <v>23</v>
       </c>
       <c r="X155" s="104" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B156" s="97" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C156" s="138">
         <v>17460152</v>
@@ -14285,7 +14316,7 @@
         <v>23</v>
       </c>
       <c r="X156" s="104" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="157" spans="2:24" x14ac:dyDescent="0.3">
@@ -14354,7 +14385,7 @@
         <v>23</v>
       </c>
       <c r="X157" s="104" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" spans="2:24" x14ac:dyDescent="0.3">
@@ -14363,7 +14394,7 @@
         <v>17460278</v>
       </c>
       <c r="D158" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E158" s="106">
         <v>20</v>
@@ -14403,7 +14434,7 @@
       <c r="R158" s="130"/>
       <c r="S158" s="130"/>
       <c r="T158" s="130" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="U158" s="110"/>
       <c r="V158" s="110" t="s">
@@ -14413,7 +14444,7 @@
         <v>23</v>
       </c>
       <c r="X158" s="111" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="2:24" x14ac:dyDescent="0.3">
@@ -14476,7 +14507,7 @@
       </c>
       <c r="W159" s="2"/>
       <c r="X159" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.3">
@@ -14541,7 +14572,7 @@
         <v>23</v>
       </c>
       <c r="X160" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="161" spans="2:24" x14ac:dyDescent="0.3">
@@ -14606,7 +14637,7 @@
         <v>23</v>
       </c>
       <c r="X161" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:24" x14ac:dyDescent="0.3">
@@ -14663,7 +14694,7 @@
         <v>23</v>
       </c>
       <c r="X162" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="163" spans="2:24" x14ac:dyDescent="0.3">
@@ -14728,7 +14759,7 @@
       </c>
       <c r="W163" s="2"/>
       <c r="X163" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="164" spans="2:24" x14ac:dyDescent="0.3">
@@ -14791,7 +14822,7 @@
       </c>
       <c r="W164" s="2"/>
       <c r="X164" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="165" spans="2:24" x14ac:dyDescent="0.3">
@@ -14856,7 +14887,7 @@
         <v>23</v>
       </c>
       <c r="X165" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="166" spans="2:24" x14ac:dyDescent="0.3">
@@ -14921,7 +14952,7 @@
         <v>23</v>
       </c>
       <c r="X166" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="167" spans="2:24" x14ac:dyDescent="0.3">
@@ -14978,7 +15009,7 @@
         <v>23</v>
       </c>
       <c r="X167" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="168" spans="2:24" x14ac:dyDescent="0.3">
@@ -15045,7 +15076,7 @@
         <v>23</v>
       </c>
       <c r="X168" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="169" spans="2:24" x14ac:dyDescent="0.3">
@@ -15100,7 +15131,7 @@
       </c>
       <c r="W169" s="2"/>
       <c r="X169" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="170" spans="2:24" x14ac:dyDescent="0.3">
@@ -15165,7 +15196,7 @@
       </c>
       <c r="W170" s="2"/>
       <c r="X170" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="171" spans="2:24" x14ac:dyDescent="0.3">
@@ -15230,7 +15261,7 @@
       </c>
       <c r="W171" s="2"/>
       <c r="X171" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="172" spans="2:24" x14ac:dyDescent="0.3">
@@ -15295,7 +15326,7 @@
       </c>
       <c r="W172" s="2"/>
       <c r="X172" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="173" spans="2:24" x14ac:dyDescent="0.3">
@@ -15360,7 +15391,7 @@
       </c>
       <c r="W173" s="2"/>
       <c r="X173" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="174" spans="2:24" x14ac:dyDescent="0.3">
@@ -15425,7 +15456,7 @@
       </c>
       <c r="W174" s="2"/>
       <c r="X174" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="175" spans="2:24" x14ac:dyDescent="0.3">
@@ -15490,7 +15521,7 @@
       </c>
       <c r="W175" s="2"/>
       <c r="X175" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="176" spans="2:24" x14ac:dyDescent="0.3">
@@ -15557,7 +15588,7 @@
         <v>23</v>
       </c>
       <c r="X176" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="177" spans="2:24" x14ac:dyDescent="0.3">
@@ -15622,7 +15653,7 @@
         <v>23</v>
       </c>
       <c r="X177" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="178" spans="2:24" x14ac:dyDescent="0.3">
@@ -15687,12 +15718,12 @@
         <v>23</v>
       </c>
       <c r="X178" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B179" s="47" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C179" s="34"/>
       <c r="D179" s="8" t="s">
@@ -15744,7 +15775,7 @@
         <v>900</v>
       </c>
       <c r="T179" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="U179" s="2"/>
       <c r="V179" s="2" t="s">
@@ -15754,7 +15785,7 @@
         <v>23</v>
       </c>
       <c r="X179" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="180" spans="2:24" x14ac:dyDescent="0.3">
@@ -15811,7 +15842,7 @@
       </c>
       <c r="W180" s="2"/>
       <c r="X180" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="181" spans="2:24" x14ac:dyDescent="0.3">
@@ -15868,7 +15899,7 @@
       </c>
       <c r="W181" s="2"/>
       <c r="X181" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="182" spans="2:24" x14ac:dyDescent="0.3">
@@ -15933,7 +15964,7 @@
       </c>
       <c r="W182" s="2"/>
       <c r="X182" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="183" spans="2:24" x14ac:dyDescent="0.3">
@@ -15998,12 +16029,12 @@
       </c>
       <c r="W183" s="2"/>
       <c r="X183" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="184" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B184" s="47" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C184" s="34"/>
       <c r="D184" s="8" t="s">
@@ -16055,7 +16086,7 @@
         <v>850</v>
       </c>
       <c r="T184" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="U184" s="2"/>
       <c r="V184" s="2" t="s">
@@ -16065,7 +16096,7 @@
         <v>23</v>
       </c>
       <c r="X184" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="185" spans="2:24" x14ac:dyDescent="0.3">
@@ -16130,7 +16161,7 @@
         <v>23</v>
       </c>
       <c r="X185" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="186" spans="2:24" x14ac:dyDescent="0.3">
@@ -16195,12 +16226,12 @@
         <v>23</v>
       </c>
       <c r="X186" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="187" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B187" s="47" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C187" s="34"/>
       <c r="D187" s="8" t="s">
@@ -16252,7 +16283,7 @@
         <v>830</v>
       </c>
       <c r="T187" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="U187" s="2"/>
       <c r="V187" s="2" t="s">
@@ -16262,7 +16293,7 @@
         <v>23</v>
       </c>
       <c r="X187" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188" spans="2:24" x14ac:dyDescent="0.3">
@@ -16317,7 +16348,7 @@
         <v>900</v>
       </c>
       <c r="T188" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="U188" s="2"/>
       <c r="V188" s="2" t="s">
@@ -16327,7 +16358,7 @@
         <v>23</v>
       </c>
       <c r="X188" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="189" spans="2:24" x14ac:dyDescent="0.3">
@@ -16394,7 +16425,7 @@
         <v>23</v>
       </c>
       <c r="X189" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="190" spans="2:24" x14ac:dyDescent="0.3">
@@ -16459,12 +16490,12 @@
         <v>23</v>
       </c>
       <c r="X190" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="191" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B191" s="47" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C191" s="34"/>
       <c r="D191" s="8" t="s">
@@ -16526,7 +16557,7 @@
         <v>23</v>
       </c>
       <c r="X191" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="192" spans="2:24" x14ac:dyDescent="0.3">
@@ -16591,7 +16622,7 @@
         <v>23</v>
       </c>
       <c r="X192" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="193" spans="2:24" x14ac:dyDescent="0.3">
@@ -16658,7 +16689,7 @@
         <v>23</v>
       </c>
       <c r="X193" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="194" spans="2:24" x14ac:dyDescent="0.3">
@@ -16723,7 +16754,7 @@
         <v>23</v>
       </c>
       <c r="X194" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="195" spans="2:24" x14ac:dyDescent="0.3">
@@ -16788,7 +16819,7 @@
         <v>23</v>
       </c>
       <c r="X195" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="196" spans="2:24" x14ac:dyDescent="0.3">
@@ -16845,7 +16876,7 @@
         <v>23</v>
       </c>
       <c r="X196" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -16899,13 +16930,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E1" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="F1" s="52"/>
       <c r="G1" s="52"/>
@@ -16927,7 +16958,7 @@
       <c r="W1" s="52"/>
       <c r="X1" s="52"/>
       <c r="Y1" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -17423,7 +17454,7 @@
       <c r="B14" s="70"/>
       <c r="C14" s="73"/>
       <c r="D14" s="52" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E14" s="52"/>
       <c r="F14" s="52"/>
@@ -17449,7 +17480,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B15" s="70"/>
       <c r="C15" s="87" t="s">
@@ -17515,7 +17546,7 @@
       </c>
       <c r="B17" s="70"/>
       <c r="C17" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
@@ -17546,7 +17577,7 @@
       </c>
       <c r="B18" s="70"/>
       <c r="C18" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D18" s="52"/>
       <c r="E18" s="52"/>
@@ -17609,7 +17640,7 @@
       <c r="B20" s="70"/>
       <c r="C20" s="73"/>
       <c r="D20" s="12" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E20" s="52"/>
       <c r="F20" s="52"/>
@@ -17638,7 +17669,7 @@
       <c r="B21" s="70"/>
       <c r="C21" s="73"/>
       <c r="D21" s="12" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E21" s="52"/>
       <c r="F21" s="52"/>
@@ -17667,7 +17698,7 @@
       <c r="B22" s="70"/>
       <c r="C22" s="73"/>
       <c r="D22" s="12" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E22" s="52"/>
       <c r="F22" s="52"/>
@@ -17696,7 +17727,7 @@
       <c r="B23" s="70"/>
       <c r="C23" s="73"/>
       <c r="D23" s="12" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
@@ -18123,7 +18154,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="79" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C38" s="80"/>
       <c r="D38" s="52"/>
@@ -18379,7 +18410,7 @@
       <c r="B44" s="70"/>
       <c r="C44" s="73"/>
       <c r="D44" s="52" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E44" s="52"/>
       <c r="F44" s="52"/>
@@ -18405,11 +18436,11 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B45" s="70"/>
       <c r="C45" s="87" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D45" s="52"/>
       <c r="E45" s="52"/>
@@ -18498,7 +18529,7 @@
       </c>
       <c r="B48" s="70"/>
       <c r="C48" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
@@ -18529,7 +18560,7 @@
       </c>
       <c r="B49" s="70"/>
       <c r="C49" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52"/>
@@ -18619,7 +18650,7 @@
       <c r="B52" s="70"/>
       <c r="C52" s="73"/>
       <c r="D52" s="52" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E52" s="52"/>
       <c r="F52" s="52"/>
@@ -18648,7 +18679,7 @@
       <c r="B53" s="70"/>
       <c r="C53" s="73"/>
       <c r="D53" s="52" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
@@ -18677,7 +18708,7 @@
       <c r="B54" s="70"/>
       <c r="C54" s="73"/>
       <c r="D54" s="52" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E54" s="52"/>
       <c r="F54" s="52"/>
@@ -19413,7 +19444,7 @@
       <c r="B76" s="70"/>
       <c r="C76" s="73"/>
       <c r="D76" s="52" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E76" s="52"/>
       <c r="F76" s="52"/>
@@ -19439,7 +19470,7 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B77" s="70"/>
       <c r="C77" s="87" t="s">
@@ -19532,7 +19563,7 @@
       </c>
       <c r="B80" s="70"/>
       <c r="C80" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D80" s="52"/>
       <c r="E80" s="52"/>
@@ -19563,7 +19594,7 @@
       </c>
       <c r="B81" s="70"/>
       <c r="C81" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D81" s="52"/>
       <c r="E81" s="52"/>
@@ -19621,11 +19652,11 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" s="29" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B83" s="70"/>
       <c r="C83" s="73" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -19657,7 +19688,7 @@
       <c r="B84" s="70"/>
       <c r="C84" s="73"/>
       <c r="D84" s="12" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E84" s="52"/>
       <c r="F84" s="52"/>
@@ -19686,7 +19717,7 @@
       <c r="B85" s="70"/>
       <c r="C85" s="73"/>
       <c r="D85" s="12" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E85" s="52"/>
       <c r="F85" s="52"/>
@@ -19715,7 +19746,7 @@
       <c r="B86" s="70"/>
       <c r="C86" s="73"/>
       <c r="D86" s="12" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E86" s="52"/>
       <c r="F86" s="52"/>
@@ -19744,7 +19775,7 @@
       <c r="B87" s="70"/>
       <c r="C87" s="73"/>
       <c r="D87" s="12" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E87" s="52"/>
       <c r="F87" s="52"/>
@@ -20326,7 +20357,9 @@
       <c r="Y105" s="52"/>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A106" s="52"/>
+      <c r="A106" s="158" t="s">
+        <v>659</v>
+      </c>
       <c r="B106" s="69"/>
       <c r="C106" s="64"/>
       <c r="E106" s="35" t="s">
@@ -20338,7 +20371,7 @@
       <c r="G106" s="36">
         <v>9</v>
       </c>
-      <c r="H106" s="37">
+      <c r="H106" s="157">
         <v>297</v>
       </c>
       <c r="I106" s="37">
@@ -20579,7 +20612,7 @@
       <c r="B111" s="70"/>
       <c r="C111" s="73"/>
       <c r="D111" s="52" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E111" s="52"/>
       <c r="F111" s="52"/>
@@ -20605,7 +20638,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B112" s="70"/>
       <c r="C112" s="87" t="s">
@@ -20698,7 +20731,7 @@
       </c>
       <c r="B115" s="70"/>
       <c r="C115" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="52"/>
@@ -20729,7 +20762,7 @@
       </c>
       <c r="B116" s="70"/>
       <c r="C116" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D116" s="52"/>
       <c r="E116" s="52"/>
@@ -20819,7 +20852,7 @@
       <c r="B119" s="70"/>
       <c r="C119" s="73"/>
       <c r="D119" s="12" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E119" s="52"/>
       <c r="F119" s="52"/>
@@ -20848,7 +20881,7 @@
       <c r="B120" s="70"/>
       <c r="C120" s="73"/>
       <c r="D120" s="12" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E120" s="52"/>
       <c r="F120" s="52"/>
@@ -20877,7 +20910,7 @@
       <c r="B121" s="70"/>
       <c r="C121" s="73"/>
       <c r="D121" s="12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E121" s="52"/>
       <c r="F121" s="52"/>
@@ -20906,7 +20939,7 @@
       <c r="B122" s="70"/>
       <c r="C122" s="73"/>
       <c r="D122" s="12" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E122" s="52"/>
       <c r="F122" s="52"/>
@@ -20997,7 +21030,7 @@
       <c r="B125" s="70"/>
       <c r="C125" s="73"/>
       <c r="D125" s="52" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E125" s="52"/>
       <c r="F125" s="52"/>
@@ -21267,7 +21300,7 @@
       </c>
       <c r="B134" s="70"/>
       <c r="C134" s="87" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D134" s="52"/>
       <c r="E134" s="52"/>
@@ -21357,7 +21390,7 @@
       <c r="B137" s="70"/>
       <c r="C137" s="73"/>
       <c r="D137" s="52" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E137" s="52"/>
       <c r="F137" s="52"/>
@@ -21718,7 +21751,7 @@
       <c r="B147" s="70"/>
       <c r="C147" s="73"/>
       <c r="D147" s="52" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E147" s="52"/>
       <c r="F147" s="52"/>
@@ -21744,7 +21777,7 @@
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B148" s="70"/>
       <c r="C148" s="87" t="s">
@@ -21837,7 +21870,7 @@
       </c>
       <c r="B151" s="70"/>
       <c r="C151" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D151" s="52"/>
       <c r="E151" s="52"/>
@@ -21868,7 +21901,7 @@
       </c>
       <c r="B152" s="70"/>
       <c r="C152" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D152" s="52"/>
       <c r="E152" s="52"/>
@@ -21958,7 +21991,7 @@
       <c r="B155" s="70"/>
       <c r="C155" s="73"/>
       <c r="D155" s="12" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E155" s="52"/>
       <c r="F155" s="52"/>
@@ -21987,7 +22020,7 @@
       <c r="B156" s="70"/>
       <c r="C156" s="73"/>
       <c r="D156" s="12" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E156" s="52"/>
       <c r="F156" s="52"/>
@@ -22016,7 +22049,7 @@
       <c r="B157" s="70"/>
       <c r="C157" s="73"/>
       <c r="D157" s="12" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E157" s="52"/>
       <c r="F157" s="52"/>
@@ -22107,7 +22140,7 @@
       <c r="B160" s="70"/>
       <c r="C160" s="73"/>
       <c r="D160" s="52" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E160" s="52"/>
       <c r="F160" s="52"/>
@@ -22709,7 +22742,7 @@
       <c r="B178" s="70"/>
       <c r="C178" s="73"/>
       <c r="D178" s="52" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E178" s="52"/>
       <c r="F178" s="52"/>
@@ -22735,7 +22768,7 @@
     </row>
     <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B179" s="70"/>
       <c r="C179" s="87" t="s">
@@ -22828,7 +22861,7 @@
       </c>
       <c r="B182" s="70"/>
       <c r="C182" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
@@ -22859,7 +22892,7 @@
       </c>
       <c r="B183" s="70"/>
       <c r="C183" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
@@ -22917,11 +22950,11 @@
     </row>
     <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185" s="29" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B185" s="70"/>
       <c r="C185" s="73" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D185" s="52"/>
       <c r="E185" s="52"/>
@@ -22953,7 +22986,7 @@
       <c r="B186" s="70"/>
       <c r="C186" s="73"/>
       <c r="D186" s="12" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E186" s="52"/>
       <c r="F186" s="52"/>
@@ -22982,7 +23015,7 @@
       <c r="B187" s="70"/>
       <c r="C187" s="73"/>
       <c r="D187" s="12" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E187" s="52"/>
       <c r="F187" s="52"/>
@@ -23011,7 +23044,7 @@
       <c r="B188" s="70"/>
       <c r="C188" s="73"/>
       <c r="D188" s="12" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E188" s="52"/>
       <c r="F188" s="52"/>
@@ -23040,7 +23073,7 @@
       <c r="B189" s="70"/>
       <c r="C189" s="73"/>
       <c r="D189" s="12" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E189" s="52"/>
       <c r="F189" s="52"/>
@@ -23649,7 +23682,7 @@
         <v>830</v>
       </c>
       <c r="U207" s="113" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="V207" s="133"/>
       <c r="W207" s="103" t="s">
@@ -23782,7 +23815,7 @@
       <c r="B211" s="70"/>
       <c r="C211" s="73"/>
       <c r="D211" s="52" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E211" s="52"/>
       <c r="F211" s="52"/>
@@ -23808,7 +23841,7 @@
     </row>
     <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B212" s="70"/>
       <c r="C212" s="87" t="s">
@@ -23901,7 +23934,7 @@
       </c>
       <c r="B215" s="70"/>
       <c r="C215" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D215" s="52"/>
       <c r="E215" s="52"/>
@@ -23932,7 +23965,7 @@
       </c>
       <c r="B216" s="70"/>
       <c r="C216" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -24022,7 +24055,7 @@
       <c r="B219" s="70"/>
       <c r="C219" s="73"/>
       <c r="D219" s="12" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E219" s="52"/>
       <c r="F219" s="52"/>
@@ -24051,7 +24084,7 @@
       <c r="B220" s="70"/>
       <c r="C220" s="73"/>
       <c r="D220" s="12" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E220" s="52"/>
       <c r="F220" s="52"/>
@@ -24080,7 +24113,7 @@
       <c r="B221" s="70"/>
       <c r="C221" s="73"/>
       <c r="D221" s="12" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E221" s="52"/>
       <c r="F221" s="52"/>
@@ -24109,7 +24142,7 @@
       <c r="B222" s="70"/>
       <c r="C222" s="73"/>
       <c r="D222" s="12" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E222" s="52"/>
       <c r="F222" s="52"/>
@@ -24470,7 +24503,7 @@
       </c>
       <c r="B234" s="70"/>
       <c r="C234" s="87" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D234" s="52"/>
       <c r="E234" s="52"/>
@@ -24560,7 +24593,7 @@
       <c r="B237" s="70"/>
       <c r="C237" s="73"/>
       <c r="D237" s="52" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E237" s="52"/>
       <c r="F237" s="52"/>
@@ -24803,7 +24836,9 @@
       <c r="Y243" s="52"/>
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A244" s="52"/>
+      <c r="A244" s="158" t="s">
+        <v>658</v>
+      </c>
       <c r="B244" s="69"/>
       <c r="C244" s="64"/>
       <c r="E244" s="35" t="s">
@@ -24815,7 +24850,7 @@
       <c r="G244" s="36">
         <v>9</v>
       </c>
-      <c r="H244" s="37">
+      <c r="H244" s="157">
         <v>296</v>
       </c>
       <c r="I244" s="37">
@@ -25056,7 +25091,7 @@
       <c r="B249" s="70"/>
       <c r="C249" s="73"/>
       <c r="D249" s="52" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E249" s="52"/>
       <c r="F249" s="52"/>
@@ -25082,7 +25117,7 @@
     </row>
     <row r="250" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A250" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B250" s="70"/>
       <c r="C250" s="87" t="s">
@@ -25296,7 +25331,7 @@
       <c r="B257" s="70"/>
       <c r="C257" s="73"/>
       <c r="D257" s="12" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E257" s="52"/>
       <c r="F257" s="52"/>
@@ -25325,7 +25360,7 @@
       <c r="B258" s="70"/>
       <c r="C258" s="73"/>
       <c r="D258" s="12" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E258" s="52"/>
       <c r="F258" s="52"/>
@@ -25354,7 +25389,7 @@
       <c r="B259" s="70"/>
       <c r="C259" s="73"/>
       <c r="D259" s="12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E259" s="52"/>
       <c r="F259" s="52"/>
@@ -25383,7 +25418,7 @@
       <c r="B260" s="70"/>
       <c r="C260" s="73"/>
       <c r="D260" s="12" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E260" s="52"/>
       <c r="F260" s="52"/>
@@ -25714,7 +25749,7 @@
       <c r="B271" s="70"/>
       <c r="C271" s="73"/>
       <c r="D271" s="52" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E271" s="52"/>
       <c r="F271" s="52"/>
@@ -25983,7 +26018,9 @@
       <c r="Y278" s="52"/>
     </row>
     <row r="279" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A279" s="52"/>
+      <c r="A279" s="158" t="s">
+        <v>657</v>
+      </c>
       <c r="B279" s="69"/>
       <c r="C279" s="64"/>
       <c r="E279" s="35" t="s">
@@ -25995,7 +26032,7 @@
       <c r="G279" s="36">
         <v>9</v>
       </c>
-      <c r="H279" s="37">
+      <c r="H279" s="157">
         <v>309</v>
       </c>
       <c r="I279" s="37">
@@ -27090,7 +27127,7 @@
     </row>
     <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B298" s="70"/>
       <c r="C298" s="87" t="s">
@@ -27183,7 +27220,7 @@
       </c>
       <c r="B301" s="70"/>
       <c r="C301" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D301" s="52"/>
       <c r="E301" s="52"/>
@@ -27214,7 +27251,7 @@
       </c>
       <c r="B302" s="70"/>
       <c r="C302" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D302" s="52"/>
       <c r="E302" s="52"/>
@@ -27304,7 +27341,7 @@
       <c r="B305" s="70"/>
       <c r="C305" s="73"/>
       <c r="D305" s="52" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E305" s="52"/>
       <c r="F305" s="52"/>
@@ -27333,7 +27370,7 @@
       <c r="B306" s="70"/>
       <c r="C306" s="73"/>
       <c r="D306" s="52" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E306" s="52"/>
       <c r="F306" s="52"/>
@@ -27362,7 +27399,7 @@
       <c r="B307" s="70"/>
       <c r="C307" s="73"/>
       <c r="D307" s="52" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E307" s="52"/>
       <c r="F307" s="52"/>
@@ -27391,7 +27428,7 @@
       <c r="B308" s="70"/>
       <c r="C308" s="73"/>
       <c r="D308" s="52" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E308" s="52"/>
       <c r="F308" s="52"/>
@@ -27420,7 +27457,7 @@
       <c r="B309" s="70"/>
       <c r="C309" s="73"/>
       <c r="D309" s="52" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E309" s="52"/>
       <c r="F309" s="52"/>
@@ -27449,7 +27486,7 @@
       <c r="B310" s="70"/>
       <c r="C310" s="73"/>
       <c r="D310" s="52" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E310" s="52"/>
       <c r="F310" s="52"/>
@@ -27540,7 +27577,7 @@
       <c r="B313" s="70"/>
       <c r="C313" s="73"/>
       <c r="D313" s="52" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E313" s="52"/>
       <c r="F313" s="52"/>
@@ -27660,7 +27697,7 @@
       <c r="B317" s="70"/>
       <c r="C317" s="73"/>
       <c r="D317" s="52" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E317" s="52"/>
       <c r="F317" s="52"/>
@@ -27900,7 +27937,7 @@
       <c r="B325" s="70"/>
       <c r="C325" s="73"/>
       <c r="D325" s="52" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E325" s="52"/>
       <c r="F325" s="52"/>
@@ -28203,7 +28240,7 @@
       <c r="B333" s="69"/>
       <c r="C333" s="64"/>
       <c r="E333" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F333" s="106">
         <v>20</v>
@@ -28243,7 +28280,7 @@
       <c r="S333" s="106"/>
       <c r="T333" s="106"/>
       <c r="U333" s="106" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="V333" s="110"/>
       <c r="W333" s="110" t="s">
@@ -28342,7 +28379,7 @@
     </row>
     <row r="337" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A337" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B337" s="70"/>
       <c r="C337" s="87" t="s">
@@ -28435,7 +28472,7 @@
       </c>
       <c r="B340" s="70"/>
       <c r="C340" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D340" s="52"/>
       <c r="E340" s="52"/>
@@ -28466,7 +28503,7 @@
       </c>
       <c r="B341" s="70"/>
       <c r="C341" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D341" s="52"/>
       <c r="E341" s="52"/>
@@ -28585,7 +28622,7 @@
       <c r="B345" s="70"/>
       <c r="C345" s="73"/>
       <c r="D345" s="78" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E345" s="52"/>
       <c r="F345" s="52"/>
@@ -28614,7 +28651,7 @@
       <c r="B346" s="70"/>
       <c r="C346" s="73"/>
       <c r="D346" s="78" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E346" s="52"/>
       <c r="F346" s="52"/>
@@ -28643,7 +28680,7 @@
       <c r="B347" s="70"/>
       <c r="C347" s="73"/>
       <c r="D347" s="78" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E347" s="52"/>
       <c r="F347" s="52"/>
@@ -28672,7 +28709,7 @@
       <c r="B348" s="70"/>
       <c r="C348" s="73"/>
       <c r="D348" s="78" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E348" s="52"/>
       <c r="F348" s="52"/>
@@ -28763,7 +28800,7 @@
       <c r="B351" s="70"/>
       <c r="C351" s="73"/>
       <c r="D351" s="52" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E351" s="52"/>
       <c r="F351" s="52"/>
@@ -29033,7 +29070,7 @@
       </c>
       <c r="B360" s="70"/>
       <c r="C360" s="87" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D360" s="52"/>
       <c r="E360" s="52"/>
@@ -29634,7 +29671,7 @@
       <c r="B372" s="69"/>
       <c r="C372" s="64"/>
       <c r="E372" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="F372" s="106">
         <v>16</v>
@@ -29682,7 +29719,7 @@
         <v>830</v>
       </c>
       <c r="U372" s="106" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="V372" s="110"/>
       <c r="W372" s="110" t="s">
@@ -29696,7 +29733,7 @@
       <c r="B373" s="69"/>
       <c r="C373" s="64"/>
       <c r="E373" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="F373" s="106">
         <v>18</v>
@@ -29817,7 +29854,7 @@
       <c r="B376" s="70"/>
       <c r="C376" s="73"/>
       <c r="D376" s="52" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E376" s="52"/>
       <c r="F376" s="52"/>
@@ -29843,7 +29880,7 @@
     </row>
     <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B377" s="70"/>
       <c r="C377" s="87" t="s">
@@ -29936,7 +29973,7 @@
       </c>
       <c r="B380" s="70"/>
       <c r="C380" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D380" s="52"/>
       <c r="E380" s="52"/>
@@ -29967,7 +30004,7 @@
       </c>
       <c r="B381" s="70"/>
       <c r="C381" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D381" s="52"/>
       <c r="E381" s="52"/>
@@ -30057,7 +30094,7 @@
       <c r="B384" s="70"/>
       <c r="C384" s="73"/>
       <c r="D384" s="78" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E384" s="52"/>
       <c r="F384" s="52"/>
@@ -30086,7 +30123,7 @@
       <c r="B385" s="70"/>
       <c r="C385" s="73"/>
       <c r="D385" s="78" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E385" s="52"/>
       <c r="F385" s="52"/>
@@ -30115,7 +30152,7 @@
       <c r="B386" s="70"/>
       <c r="C386" s="73"/>
       <c r="D386" s="78" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E386" s="52"/>
       <c r="F386" s="52"/>
@@ -30144,7 +30181,7 @@
       <c r="B387" s="70"/>
       <c r="C387" s="73"/>
       <c r="D387" s="78" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E387" s="52"/>
       <c r="F387" s="52"/>
@@ -30173,7 +30210,7 @@
       <c r="B388" s="70"/>
       <c r="C388" s="73"/>
       <c r="D388" s="78" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E388" s="52"/>
       <c r="F388" s="52"/>
@@ -30264,7 +30301,7 @@
       <c r="B391" s="70"/>
       <c r="C391" s="73"/>
       <c r="D391" s="52" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E391" s="52"/>
       <c r="F391" s="52"/>
@@ -30504,7 +30541,7 @@
       <c r="B399" s="70"/>
       <c r="C399" s="73"/>
       <c r="D399" s="52" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E399" s="52"/>
       <c r="F399" s="52"/>
@@ -31002,7 +31039,7 @@
       <c r="B411" s="70"/>
       <c r="C411" s="73"/>
       <c r="D411" s="52" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E411" s="52"/>
       <c r="F411" s="52"/>
@@ -31028,7 +31065,7 @@
     </row>
     <row r="412" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A412" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B412" s="70"/>
       <c r="C412" s="87" t="s">
@@ -31121,7 +31158,7 @@
       </c>
       <c r="B415" s="70"/>
       <c r="C415" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D415" s="52"/>
       <c r="E415" s="52"/>
@@ -31152,7 +31189,7 @@
       </c>
       <c r="B416" s="70"/>
       <c r="C416" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D416" s="52"/>
       <c r="E416" s="52"/>
@@ -31242,7 +31279,7 @@
       <c r="B419" s="70"/>
       <c r="C419" s="73"/>
       <c r="D419" s="78" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E419" s="52"/>
       <c r="F419" s="52"/>
@@ -31271,7 +31308,7 @@
       <c r="B420" s="70"/>
       <c r="C420" s="73"/>
       <c r="D420" s="78" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E420" s="52"/>
       <c r="F420" s="52"/>
@@ -31300,7 +31337,7 @@
       <c r="B421" s="70"/>
       <c r="C421" s="73"/>
       <c r="D421" s="78" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E421" s="52"/>
       <c r="F421" s="52"/>
@@ -31329,7 +31366,7 @@
       <c r="B422" s="70"/>
       <c r="C422" s="73"/>
       <c r="D422" s="78" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E422" s="52"/>
       <c r="F422" s="52"/>
@@ -31358,7 +31395,7 @@
       <c r="B423" s="70"/>
       <c r="C423" s="73"/>
       <c r="D423" s="78" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E423" s="52"/>
       <c r="F423" s="52"/>
@@ -31569,7 +31606,7 @@
       <c r="B430" s="70"/>
       <c r="C430" s="73"/>
       <c r="D430" s="52" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E430" s="52"/>
       <c r="F430" s="52"/>
@@ -31689,7 +31726,7 @@
       <c r="B434" s="70"/>
       <c r="C434" s="73"/>
       <c r="D434" s="52" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E434" s="52"/>
       <c r="F434" s="52"/>
@@ -31803,7 +31840,7 @@
         <v>0</v>
       </c>
       <c r="B438" s="79" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C438" s="80"/>
       <c r="D438" s="52"/>
@@ -32046,7 +32083,7 @@
         <v>830</v>
       </c>
       <c r="U442" s="106" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="V442" s="110"/>
       <c r="W442" s="110" t="s">
@@ -32118,11 +32155,11 @@
       </c>
       <c r="B445" s="70"/>
       <c r="C445" s="73"/>
-      <c r="D445" s="147" t="s">
-        <v>652</v>
-      </c>
-      <c r="E445" s="147"/>
-      <c r="F445" s="147"/>
+      <c r="D445" s="146" t="s">
+        <v>647</v>
+      </c>
+      <c r="E445" s="146"/>
+      <c r="F445" s="146"/>
       <c r="G445" s="52"/>
       <c r="H445" s="52"/>
       <c r="I445" s="52"/>
@@ -32145,11 +32182,11 @@
     </row>
     <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B446" s="70"/>
       <c r="C446" s="87" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D446" s="52"/>
       <c r="E446" s="52"/>
@@ -32207,7 +32244,9 @@
       </c>
       <c r="B448" s="70"/>
       <c r="C448" s="80"/>
-      <c r="D448" s="146"/>
+      <c r="D448" s="52" t="s">
+        <v>53</v>
+      </c>
       <c r="E448" s="52"/>
       <c r="F448" s="52"/>
       <c r="G448" s="52"/>
@@ -32236,7 +32275,7 @@
       </c>
       <c r="B449" s="70"/>
       <c r="C449" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D449" s="52"/>
       <c r="E449" s="52"/>
@@ -32267,7 +32306,7 @@
       </c>
       <c r="B450" s="70"/>
       <c r="C450" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D450" s="52"/>
       <c r="E450" s="52"/>
@@ -32495,7 +32534,9 @@
       </c>
       <c r="B458" s="70"/>
       <c r="C458" s="73"/>
-      <c r="D458" s="52"/>
+      <c r="D458" s="52" t="s">
+        <v>652</v>
+      </c>
       <c r="E458" s="52"/>
       <c r="F458" s="52"/>
       <c r="G458" s="52"/>
@@ -32524,7 +32565,9 @@
       </c>
       <c r="B459" s="70"/>
       <c r="C459" s="73"/>
-      <c r="D459" s="52"/>
+      <c r="D459" s="52" t="s">
+        <v>653</v>
+      </c>
       <c r="E459" s="52"/>
       <c r="F459" s="52"/>
       <c r="G459" s="52"/>
@@ -32553,7 +32596,7 @@
       </c>
       <c r="B460" s="70"/>
       <c r="C460" s="87" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D460" s="52"/>
       <c r="E460" s="52"/>
@@ -32611,7 +32654,9 @@
       </c>
       <c r="B462" s="70"/>
       <c r="C462" s="73"/>
-      <c r="D462" s="52"/>
+      <c r="D462" s="52" t="s">
+        <v>654</v>
+      </c>
       <c r="E462" s="52"/>
       <c r="F462" s="52"/>
       <c r="G462" s="52"/>
@@ -32640,7 +32685,9 @@
       </c>
       <c r="B463" s="70"/>
       <c r="C463" s="73"/>
-      <c r="D463" s="52"/>
+      <c r="D463" s="156" t="s">
+        <v>655</v>
+      </c>
       <c r="E463" s="52"/>
       <c r="F463" s="52"/>
       <c r="G463" s="52"/>
@@ -32669,7 +32716,7 @@
       </c>
       <c r="B464" s="70"/>
       <c r="C464" s="87" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D464" s="52"/>
       <c r="E464" s="52"/>
@@ -32727,7 +32774,9 @@
       </c>
       <c r="B466" s="70"/>
       <c r="C466" s="73"/>
-      <c r="D466" s="52"/>
+      <c r="D466" s="52" t="s">
+        <v>159</v>
+      </c>
       <c r="E466" s="52"/>
       <c r="F466" s="52"/>
       <c r="G466" s="52"/>
@@ -32756,7 +32805,9 @@
       </c>
       <c r="B467" s="70"/>
       <c r="C467" s="73"/>
-      <c r="D467" s="52"/>
+      <c r="D467" s="156" t="s">
+        <v>656</v>
+      </c>
       <c r="E467" s="52"/>
       <c r="F467" s="52"/>
       <c r="G467" s="52"/>
@@ -32785,7 +32836,7 @@
       </c>
       <c r="B468" s="70"/>
       <c r="C468" s="87" t="s">
-        <v>656</v>
+        <v>592</v>
       </c>
       <c r="D468" s="52"/>
       <c r="E468" s="52"/>
@@ -33194,7 +33245,7 @@
       <c r="B477" s="69"/>
       <c r="C477" s="64"/>
       <c r="E477" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="F477" s="106">
         <v>18</v>
@@ -33320,7 +33371,7 @@
       <c r="B479" s="69"/>
       <c r="C479" s="64"/>
       <c r="E479" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F479" s="106">
         <v>24</v>
@@ -33599,7 +33650,7 @@
       <c r="B485" s="70"/>
       <c r="C485" s="73"/>
       <c r="D485" s="52" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E485" s="52"/>
       <c r="F485" s="52"/>
@@ -33625,7 +33676,7 @@
     </row>
     <row r="486" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A486" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B486" s="70"/>
       <c r="C486" s="87" t="s">
@@ -33718,7 +33769,7 @@
       </c>
       <c r="B489" s="70"/>
       <c r="C489" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D489" s="52"/>
       <c r="E489" s="52"/>
@@ -33749,7 +33800,7 @@
       </c>
       <c r="B490" s="70"/>
       <c r="C490" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D490" s="52"/>
       <c r="E490" s="52"/>
@@ -33839,7 +33890,7 @@
       <c r="B493" s="70"/>
       <c r="C493" s="73"/>
       <c r="D493" s="78" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E493" s="52"/>
       <c r="F493" s="52"/>
@@ -33868,7 +33919,7 @@
       <c r="B494" s="70"/>
       <c r="C494" s="73"/>
       <c r="D494" s="78" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E494" s="52"/>
       <c r="F494" s="52"/>
@@ -33897,7 +33948,7 @@
       <c r="B495" s="70"/>
       <c r="C495" s="73"/>
       <c r="D495" s="78" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E495" s="52"/>
       <c r="F495" s="52"/>
@@ -33926,7 +33977,7 @@
       <c r="B496" s="70"/>
       <c r="C496" s="73"/>
       <c r="D496" s="78" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E496" s="52"/>
       <c r="F496" s="52"/>
@@ -33955,7 +34006,7 @@
       <c r="B497" s="70"/>
       <c r="C497" s="73"/>
       <c r="D497" s="78" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E497" s="52"/>
       <c r="F497" s="52"/>
@@ -34046,7 +34097,7 @@
       <c r="B500" s="70"/>
       <c r="C500" s="73"/>
       <c r="D500" s="52" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E500" s="52"/>
       <c r="F500" s="52"/>
@@ -34166,7 +34217,7 @@
       <c r="B504" s="70"/>
       <c r="C504" s="73"/>
       <c r="D504" s="52" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E504" s="52"/>
       <c r="F504" s="52"/>
@@ -34286,7 +34337,7 @@
       <c r="B508" s="70"/>
       <c r="C508" s="73"/>
       <c r="D508" s="52" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E508" s="52"/>
       <c r="F508" s="52"/>
@@ -34316,7 +34367,7 @@
       </c>
       <c r="B509" s="70"/>
       <c r="C509" s="87" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D509" s="52"/>
       <c r="E509" s="52"/>
@@ -34400,7 +34451,7 @@
         <v>0</v>
       </c>
       <c r="B512" s="79" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C512" s="80"/>
       <c r="D512" s="52"/>
@@ -34533,7 +34584,7 @@
       <c r="B515" s="69"/>
       <c r="C515" s="64"/>
       <c r="E515" s="98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F515" s="98">
         <v>16</v>
@@ -34917,7 +34968,7 @@
       <c r="B521" s="69"/>
       <c r="C521" s="64"/>
       <c r="E521" s="106" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="F521" s="106">
         <v>16</v>
@@ -35038,7 +35089,7 @@
       <c r="B524" s="70"/>
       <c r="C524" s="73"/>
       <c r="D524" s="52" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E524" s="52"/>
       <c r="F524" s="52"/>
@@ -35064,11 +35115,11 @@
     </row>
     <row r="525" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A525" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B525" s="70"/>
       <c r="C525" s="87" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D525" s="52"/>
       <c r="E525" s="52"/>
@@ -35157,7 +35208,7 @@
       </c>
       <c r="B528" s="70"/>
       <c r="C528" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D528" s="52"/>
       <c r="E528" s="52"/>
@@ -35188,7 +35239,7 @@
       </c>
       <c r="B529" s="70"/>
       <c r="C529" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D529" s="52"/>
       <c r="E529" s="52"/>
@@ -35247,7 +35298,7 @@
       <c r="B531" s="70"/>
       <c r="C531" s="73"/>
       <c r="D531" s="12" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E531" s="52"/>
       <c r="F531" s="52"/>
@@ -35276,7 +35327,7 @@
       <c r="B532" s="70"/>
       <c r="C532" s="73"/>
       <c r="D532" s="12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E532" s="52"/>
       <c r="F532" s="52"/>
@@ -35305,7 +35356,7 @@
       <c r="B533" s="70"/>
       <c r="C533" s="73"/>
       <c r="D533" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E533" s="52"/>
       <c r="F533" s="52"/>
@@ -35334,7 +35385,7 @@
       <c r="B534" s="70"/>
       <c r="C534" s="73"/>
       <c r="D534" s="12" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E534" s="52"/>
       <c r="F534" s="52"/>
@@ -35363,7 +35414,7 @@
       <c r="B535" s="70"/>
       <c r="C535" s="73"/>
       <c r="D535" s="12" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E535" s="52"/>
       <c r="F535" s="52"/>
@@ -35392,7 +35443,7 @@
       <c r="B536" s="70"/>
       <c r="C536" s="73"/>
       <c r="D536" s="12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E536" s="52"/>
       <c r="F536" s="52"/>
@@ -36162,7 +36213,7 @@
     </row>
     <row r="559" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A559" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B559" s="70"/>
       <c r="C559" s="87" t="s">
@@ -36255,7 +36306,7 @@
       </c>
       <c r="B562" s="70"/>
       <c r="C562" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D562" s="52"/>
       <c r="E562" s="52"/>
@@ -36286,7 +36337,7 @@
       </c>
       <c r="B563" s="70"/>
       <c r="C563" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D563" s="52"/>
       <c r="E563" s="52"/>
@@ -36313,11 +36364,11 @@
     </row>
     <row r="564" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A564" s="29" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B564" s="70"/>
       <c r="C564" s="73" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D564" s="52"/>
       <c r="E564" s="52"/>
@@ -36349,7 +36400,7 @@
       <c r="B565" s="70"/>
       <c r="C565" s="73"/>
       <c r="D565" s="78" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E565" s="52"/>
       <c r="F565" s="52"/>
@@ -36378,7 +36429,7 @@
       <c r="B566" s="70"/>
       <c r="C566" s="73"/>
       <c r="D566" s="78" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E566" s="52"/>
       <c r="F566" s="52"/>
@@ -36407,7 +36458,7 @@
       <c r="B567" s="70"/>
       <c r="C567" s="73"/>
       <c r="D567" s="78" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E567" s="52"/>
       <c r="F567" s="52"/>
@@ -36436,7 +36487,7 @@
       <c r="B568" s="70"/>
       <c r="C568" s="73"/>
       <c r="D568" s="78" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E568" s="52"/>
       <c r="F568" s="52"/>
@@ -36465,7 +36516,7 @@
       <c r="B569" s="70"/>
       <c r="C569" s="73"/>
       <c r="D569" s="78" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E569" s="52"/>
       <c r="F569" s="52"/>
@@ -36891,7 +36942,7 @@
         <v>0</v>
       </c>
       <c r="B584" s="79" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C584" s="80"/>
       <c r="D584" s="52"/>
@@ -37451,7 +37502,7 @@
         <v>900</v>
       </c>
       <c r="U593" s="130" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="V593" s="110"/>
       <c r="W593" s="110" t="s">
@@ -37466,7 +37517,7 @@
       <c r="B594" s="69"/>
       <c r="C594" s="64"/>
       <c r="E594" s="106" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F594" s="106">
         <v>22</v>
@@ -37514,7 +37565,7 @@
         <v>850</v>
       </c>
       <c r="U594" s="130" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="V594" s="110"/>
       <c r="W594" s="110" t="s">
@@ -37590,7 +37641,7 @@
       <c r="B597" s="70"/>
       <c r="C597" s="73"/>
       <c r="D597" s="52" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E597" s="52"/>
       <c r="F597" s="52"/>
@@ -37617,11 +37668,11 @@
     </row>
     <row r="598" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A598" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B598" s="70"/>
       <c r="C598" s="87" t="s">
-        <v>420</v>
+        <v>209</v>
       </c>
       <c r="D598" s="52"/>
       <c r="E598" s="52"/>
@@ -37710,7 +37761,7 @@
       </c>
       <c r="B601" s="70"/>
       <c r="C601" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D601" s="52"/>
       <c r="E601" s="52"/>
@@ -37741,7 +37792,7 @@
       </c>
       <c r="B602" s="70"/>
       <c r="C602" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D602" s="52"/>
       <c r="E602" s="52"/>
@@ -37831,7 +37882,7 @@
       <c r="B605" s="70"/>
       <c r="C605" s="73"/>
       <c r="D605" s="12" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E605" s="52"/>
       <c r="F605" s="52"/>
@@ -37860,7 +37911,7 @@
       <c r="B606" s="70"/>
       <c r="C606" s="73"/>
       <c r="D606" s="12" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E606" s="52"/>
       <c r="F606" s="52"/>
@@ -37889,7 +37940,7 @@
       <c r="B607" s="70"/>
       <c r="C607" s="73"/>
       <c r="D607" s="12" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E607" s="52"/>
       <c r="F607" s="52"/>
@@ -37918,7 +37969,7 @@
       <c r="B608" s="70"/>
       <c r="C608" s="73"/>
       <c r="D608" s="12" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E608" s="52"/>
       <c r="F608" s="52"/>
@@ -37947,7 +37998,7 @@
       <c r="B609" s="70"/>
       <c r="C609" s="73"/>
       <c r="D609" s="12" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E609" s="52"/>
       <c r="F609" s="52"/>
@@ -37976,7 +38027,7 @@
       <c r="B610" s="70"/>
       <c r="C610" s="73"/>
       <c r="D610" s="12" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E610" s="52"/>
       <c r="F610" s="52"/>
@@ -38067,7 +38118,7 @@
       <c r="B613" s="70"/>
       <c r="C613" s="73"/>
       <c r="D613" s="52" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E613" s="52"/>
       <c r="F613" s="52"/>
@@ -38156,7 +38207,7 @@
       <c r="B616" s="70"/>
       <c r="C616" s="73"/>
       <c r="D616" s="52" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E616" s="52"/>
       <c r="F616" s="52"/>
@@ -38187,7 +38238,7 @@
       <c r="B617" s="70"/>
       <c r="C617" s="73"/>
       <c r="D617" s="52" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E617" s="52"/>
       <c r="F617" s="52"/>
@@ -38337,7 +38388,7 @@
       </c>
       <c r="B622" s="70"/>
       <c r="C622" s="87" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D622" s="52"/>
       <c r="E622" s="52"/>
@@ -38854,7 +38905,7 @@
         <v>900</v>
       </c>
       <c r="U632" s="130" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="V632" s="110"/>
       <c r="W632" s="110" t="s">
@@ -38868,7 +38919,7 @@
       <c r="B633" s="69"/>
       <c r="C633" s="64"/>
       <c r="E633" s="106" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F633" s="106">
         <v>22</v>
@@ -38916,7 +38967,7 @@
         <v>850</v>
       </c>
       <c r="U633" s="130" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="V633" s="110"/>
       <c r="W633" s="110" t="s">
@@ -39071,7 +39122,7 @@
     </row>
     <row r="638" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A638" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B638" s="70"/>
       <c r="C638" s="87" t="s">
@@ -39164,7 +39215,7 @@
       </c>
       <c r="B641" s="70"/>
       <c r="C641" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D641" s="52"/>
       <c r="E641" s="52"/>
@@ -39195,7 +39246,7 @@
       </c>
       <c r="B642" s="70"/>
       <c r="C642" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D642" s="52"/>
       <c r="E642" s="52"/>
@@ -39285,7 +39336,7 @@
       <c r="B645" s="70"/>
       <c r="C645" s="73"/>
       <c r="D645" s="78" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E645" s="52"/>
       <c r="F645" s="52"/>
@@ -39314,7 +39365,7 @@
       <c r="B646" s="70"/>
       <c r="C646" s="73"/>
       <c r="D646" s="78" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E646" s="52"/>
       <c r="F646" s="52"/>
@@ -39343,7 +39394,7 @@
       <c r="B647" s="70"/>
       <c r="C647" s="73"/>
       <c r="D647" s="78" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E647" s="52"/>
       <c r="F647" s="52"/>
@@ -39372,7 +39423,7 @@
       <c r="B648" s="70"/>
       <c r="C648" s="73"/>
       <c r="D648" s="78" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E648" s="52"/>
       <c r="F648" s="52"/>
@@ -39401,7 +39452,7 @@
       <c r="B649" s="70"/>
       <c r="C649" s="73"/>
       <c r="D649" s="78" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E649" s="52"/>
       <c r="F649" s="52"/>
@@ -39430,7 +39481,7 @@
       <c r="B650" s="70"/>
       <c r="C650" s="73"/>
       <c r="D650" s="78" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E650" s="52"/>
       <c r="F650" s="52"/>
@@ -39459,7 +39510,7 @@
       <c r="B651" s="70"/>
       <c r="C651" s="73"/>
       <c r="D651" s="78" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E651" s="52"/>
       <c r="F651" s="52"/>
@@ -39550,7 +39601,7 @@
       <c r="B654" s="70"/>
       <c r="C654" s="73"/>
       <c r="D654" s="52" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E654" s="52"/>
       <c r="F654" s="52"/>
@@ -39820,7 +39871,7 @@
       </c>
       <c r="B663" s="70"/>
       <c r="C663" s="87" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D663" s="52"/>
       <c r="E663" s="52"/>
@@ -40101,7 +40152,7 @@
       <c r="A670" s="52"/>
       <c r="C670" s="64"/>
       <c r="E670" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F670" s="106">
         <v>20</v>
@@ -40141,7 +40192,7 @@
       <c r="S670" s="130"/>
       <c r="T670" s="130"/>
       <c r="U670" s="130" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="V670" s="110"/>
       <c r="W670" s="110" t="s">
@@ -40462,7 +40513,7 @@
       <c r="B677" s="70"/>
       <c r="C677" s="73"/>
       <c r="D677" s="52" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E677" s="52"/>
       <c r="F677" s="52"/>
@@ -40488,7 +40539,7 @@
     </row>
     <row r="678" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A678" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B678" s="70"/>
       <c r="C678" s="87" t="s">
@@ -40581,7 +40632,7 @@
       </c>
       <c r="B681" s="70"/>
       <c r="C681" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D681" s="52"/>
       <c r="E681" s="52"/>
@@ -40612,7 +40663,7 @@
       </c>
       <c r="B682" s="70"/>
       <c r="C682" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D682" s="52"/>
       <c r="E682" s="52"/>
@@ -40702,7 +40753,7 @@
       <c r="B685" s="70"/>
       <c r="C685" s="73"/>
       <c r="D685" s="78" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E685" s="52"/>
       <c r="F685" s="52"/>
@@ -40731,7 +40782,7 @@
       <c r="B686" s="70"/>
       <c r="C686" s="73"/>
       <c r="D686" s="78" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E686" s="52"/>
       <c r="F686" s="52"/>
@@ -40760,7 +40811,7 @@
       <c r="B687" s="70"/>
       <c r="C687" s="73"/>
       <c r="D687" s="78" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E687" s="52"/>
       <c r="F687" s="52"/>
@@ -40789,7 +40840,7 @@
       <c r="B688" s="70"/>
       <c r="C688" s="73"/>
       <c r="D688" s="78" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E688" s="52"/>
       <c r="F688" s="52"/>
@@ -40818,7 +40869,7 @@
       <c r="B689" s="70"/>
       <c r="C689" s="73"/>
       <c r="D689" s="78" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E689" s="52"/>
       <c r="F689" s="52"/>
@@ -40847,7 +40898,7 @@
       <c r="B690" s="70"/>
       <c r="C690" s="73"/>
       <c r="D690" s="78" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E690" s="52"/>
       <c r="F690" s="52"/>
@@ -41962,7 +42013,7 @@
     </row>
     <row r="718" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A718" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B718" s="70"/>
       <c r="C718" s="87" t="s">
@@ -42055,7 +42106,7 @@
       </c>
       <c r="B721" s="70"/>
       <c r="C721" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D721" s="52"/>
       <c r="E721" s="52"/>
@@ -42086,7 +42137,7 @@
       </c>
       <c r="B722" s="70"/>
       <c r="C722" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D722" s="52"/>
       <c r="E722" s="52"/>
@@ -42176,7 +42227,7 @@
       <c r="B725" s="70"/>
       <c r="C725" s="73"/>
       <c r="D725" s="78" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E725" s="52"/>
       <c r="F725" s="52"/>
@@ -42205,7 +42256,7 @@
       <c r="B726" s="70"/>
       <c r="C726" s="73"/>
       <c r="D726" s="78" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E726" s="52"/>
       <c r="F726" s="52"/>
@@ -42234,7 +42285,7 @@
       <c r="B727" s="70"/>
       <c r="C727" s="73"/>
       <c r="D727" s="78" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E727" s="52"/>
       <c r="F727" s="52"/>
@@ -42263,7 +42314,7 @@
       <c r="B728" s="70"/>
       <c r="C728" s="73"/>
       <c r="D728" s="78" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E728" s="52"/>
       <c r="F728" s="52"/>
@@ -42292,7 +42343,7 @@
       <c r="B729" s="70"/>
       <c r="C729" s="73"/>
       <c r="D729" s="78" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E729" s="52"/>
       <c r="F729" s="52"/>
@@ -42503,7 +42554,7 @@
       <c r="B736" s="70"/>
       <c r="C736" s="73"/>
       <c r="D736" s="52" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E736" s="52"/>
       <c r="F736" s="52"/>
@@ -42533,7 +42584,7 @@
       </c>
       <c r="B737" s="70"/>
       <c r="C737" s="87" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D737" s="52"/>
       <c r="E737" s="52"/>
@@ -42623,7 +42674,7 @@
       <c r="B740" s="70"/>
       <c r="C740" s="73"/>
       <c r="D740" s="52" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E740" s="52"/>
       <c r="F740" s="52"/>
@@ -43057,7 +43108,7 @@
       <c r="B751" s="70"/>
       <c r="C751" s="73"/>
       <c r="D751" s="52" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E751" s="52"/>
       <c r="F751" s="52"/>
@@ -43083,7 +43134,7 @@
     </row>
     <row r="752" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A752" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B752" s="70"/>
       <c r="C752" s="87" t="s">
@@ -43146,7 +43197,7 @@
       <c r="B754" s="70"/>
       <c r="C754" s="80"/>
       <c r="D754" s="52" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E754" s="52"/>
       <c r="F754" s="52"/>
@@ -43176,7 +43227,7 @@
       </c>
       <c r="B755" s="70"/>
       <c r="C755" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D755" s="52"/>
       <c r="E755" s="52"/>
@@ -43207,7 +43258,7 @@
       </c>
       <c r="B756" s="70"/>
       <c r="C756" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D756" s="52"/>
       <c r="E756" s="52"/>
@@ -43297,7 +43348,7 @@
       <c r="B759" s="70"/>
       <c r="C759" s="73"/>
       <c r="D759" s="78" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E759" s="52"/>
       <c r="F759" s="52"/>
@@ -43326,7 +43377,7 @@
       <c r="B760" s="70"/>
       <c r="C760" s="73"/>
       <c r="D760" s="78" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E760" s="52"/>
       <c r="F760" s="52"/>
@@ -43355,7 +43406,7 @@
       <c r="B761" s="70"/>
       <c r="C761" s="73"/>
       <c r="D761" s="78" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E761" s="52"/>
       <c r="F761" s="52"/>
@@ -43384,7 +43435,7 @@
       <c r="B762" s="70"/>
       <c r="C762" s="73"/>
       <c r="D762" s="78" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E762" s="52"/>
       <c r="F762" s="52"/>
@@ -43413,7 +43464,7 @@
       <c r="B763" s="70"/>
       <c r="C763" s="73"/>
       <c r="D763" s="78" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E763" s="52"/>
       <c r="F763" s="52"/>
@@ -43442,7 +43493,7 @@
       <c r="B764" s="70"/>
       <c r="C764" s="73"/>
       <c r="D764" s="78" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E764" s="52"/>
       <c r="F764" s="52"/>
@@ -43533,7 +43584,7 @@
       <c r="B767" s="70"/>
       <c r="C767" s="73"/>
       <c r="D767" s="52" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E767" s="52"/>
       <c r="F767" s="52"/>
@@ -43653,7 +43704,7 @@
       <c r="B771" s="70"/>
       <c r="C771" s="73"/>
       <c r="D771" s="52" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E771" s="52"/>
       <c r="F771" s="52"/>
@@ -43773,7 +43824,7 @@
       <c r="B775" s="70"/>
       <c r="C775" s="73"/>
       <c r="D775" s="52" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E775" s="52"/>
       <c r="F775" s="52"/>
@@ -43893,7 +43944,7 @@
       <c r="B779" s="70"/>
       <c r="C779" s="73"/>
       <c r="D779" s="52" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E779" s="52"/>
       <c r="F779" s="52"/>
@@ -44139,19 +44190,19 @@
       <c r="A786" s="52"/>
       <c r="B786" s="69"/>
       <c r="C786" s="64"/>
-      <c r="E786" s="149" t="s">
+      <c r="E786" s="148" t="s">
         <v>57</v>
       </c>
-      <c r="F786" s="149">
+      <c r="F786" s="148">
         <v>16</v>
       </c>
-      <c r="G786" s="150">
+      <c r="G786" s="149">
         <v>8.25</v>
       </c>
-      <c r="H786" s="151">
+      <c r="H786" s="150">
         <v>10.9</v>
       </c>
-      <c r="I786" s="151">
+      <c r="I786" s="150">
         <v>41.4</v>
       </c>
       <c r="J786" s="129">
@@ -44160,7 +44211,7 @@
       <c r="K786" s="129">
         <v>15</v>
       </c>
-      <c r="L786" s="152">
+      <c r="L786" s="151">
         <v>19</v>
       </c>
       <c r="M786" s="129">
@@ -44181,13 +44232,13 @@
       <c r="R786" s="129">
         <v>120</v>
       </c>
-      <c r="S786" s="149">
+      <c r="S786" s="148">
         <v>2725</v>
       </c>
-      <c r="T786" s="149">
+      <c r="T786" s="148">
         <v>830</v>
       </c>
-      <c r="U786" s="149" t="s">
+      <c r="U786" s="148" t="s">
         <v>56</v>
       </c>
       <c r="V786" s="39"/>
@@ -44285,7 +44336,7 @@
     </row>
     <row r="790" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A790" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B790" s="70"/>
       <c r="C790" s="87" t="s">
@@ -44378,7 +44429,7 @@
       </c>
       <c r="B793" s="70"/>
       <c r="C793" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D793" s="52"/>
       <c r="E793" s="52"/>
@@ -44409,7 +44460,7 @@
       </c>
       <c r="B794" s="70"/>
       <c r="C794" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D794" s="52"/>
       <c r="E794" s="52"/>
@@ -44468,7 +44519,7 @@
       <c r="B796" s="70"/>
       <c r="C796" s="73"/>
       <c r="D796" s="78" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E796" s="52"/>
       <c r="F796" s="52"/>
@@ -44497,7 +44548,7 @@
       <c r="B797" s="70"/>
       <c r="C797" s="73"/>
       <c r="D797" s="78" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E797" s="52"/>
       <c r="F797" s="52"/>
@@ -44526,7 +44577,7 @@
       <c r="B798" s="70"/>
       <c r="C798" s="73"/>
       <c r="D798" s="78" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E798" s="52"/>
       <c r="F798" s="52"/>
@@ -44555,7 +44606,7 @@
       <c r="B799" s="70"/>
       <c r="C799" s="73"/>
       <c r="D799" s="78" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E799" s="52"/>
       <c r="F799" s="52"/>
@@ -44981,7 +45032,7 @@
         <v>0</v>
       </c>
       <c r="B814" s="144" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C814" s="145"/>
       <c r="D814" s="52"/>
@@ -45257,7 +45308,7 @@
     </row>
     <row r="821" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A821" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B821" s="70"/>
       <c r="C821" s="87"/>
@@ -46315,7 +46366,7 @@
       <c r="B853" s="70"/>
       <c r="C853" s="73"/>
       <c r="D853" s="52" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E853" s="52"/>
       <c r="F853" s="52"/>
@@ -46341,7 +46392,7 @@
     </row>
     <row r="854" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A854" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B854" s="70"/>
       <c r="C854" s="87" t="s">
@@ -46434,7 +46485,7 @@
       </c>
       <c r="B857" s="70"/>
       <c r="C857" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D857" s="52"/>
       <c r="E857" s="52"/>
@@ -46465,7 +46516,7 @@
       </c>
       <c r="B858" s="70"/>
       <c r="C858" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D858" s="52"/>
       <c r="E858" s="52"/>
@@ -46524,7 +46575,7 @@
       <c r="B860" s="70"/>
       <c r="C860" s="73"/>
       <c r="D860" s="78" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E860" s="52"/>
       <c r="F860" s="52"/>
@@ -46553,7 +46604,7 @@
       <c r="B861" s="70"/>
       <c r="C861" s="73"/>
       <c r="D861" s="78" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E861" s="52"/>
       <c r="F861" s="52"/>
@@ -46582,7 +46633,7 @@
       <c r="B862" s="70"/>
       <c r="C862" s="73"/>
       <c r="D862" s="78" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E862" s="52"/>
       <c r="F862" s="52"/>
@@ -47286,7 +47337,7 @@
     </row>
     <row r="884" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A884" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B884" s="70"/>
       <c r="C884" s="87" t="s">
@@ -47379,7 +47430,7 @@
       </c>
       <c r="B887" s="70"/>
       <c r="C887" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D887" s="52"/>
       <c r="E887" s="52"/>
@@ -47410,7 +47461,7 @@
       </c>
       <c r="B888" s="70"/>
       <c r="C888" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D888" s="52"/>
       <c r="E888" s="52"/>
@@ -47469,7 +47520,7 @@
       <c r="B890" s="70"/>
       <c r="C890" s="73"/>
       <c r="D890" s="78" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E890" s="52"/>
       <c r="F890" s="52"/>
@@ -47498,7 +47549,7 @@
       <c r="B891" s="70"/>
       <c r="C891" s="73"/>
       <c r="D891" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E891" s="52"/>
       <c r="F891" s="52"/>
@@ -47527,7 +47578,7 @@
       <c r="B892" s="70"/>
       <c r="C892" s="73"/>
       <c r="D892" s="78" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E892" s="52"/>
       <c r="F892" s="52"/>
@@ -47556,7 +47607,7 @@
       <c r="B893" s="70"/>
       <c r="C893" s="73"/>
       <c r="D893" s="78" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E893" s="52"/>
       <c r="F893" s="52"/>
@@ -48516,7 +48567,7 @@
     </row>
     <row r="919" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A919" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B919" s="70"/>
       <c r="C919" s="87" t="s">
@@ -48609,7 +48660,7 @@
       </c>
       <c r="B922" s="70"/>
       <c r="C922" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D922" s="52"/>
       <c r="E922" s="52"/>
@@ -48640,7 +48691,7 @@
       </c>
       <c r="B923" s="70"/>
       <c r="C923" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D923" s="52"/>
       <c r="E923" s="52"/>
@@ -48699,7 +48750,7 @@
       <c r="B925" s="70"/>
       <c r="C925" s="73"/>
       <c r="D925" s="78" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E925" s="52"/>
       <c r="F925" s="52"/>
@@ -48728,7 +48779,7 @@
       <c r="B926" s="70"/>
       <c r="C926" s="73"/>
       <c r="D926" s="78" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E926" s="52"/>
       <c r="F926" s="52"/>
@@ -48757,7 +48808,7 @@
       <c r="B927" s="70"/>
       <c r="C927" s="73"/>
       <c r="D927" s="78" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E927" s="52"/>
       <c r="F927" s="52"/>
@@ -49620,7 +49671,7 @@
     </row>
     <row r="952" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A952" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B952" s="70"/>
       <c r="C952" s="87" t="s">
@@ -49713,7 +49764,7 @@
       </c>
       <c r="B955" s="70"/>
       <c r="C955" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D955" s="52"/>
       <c r="E955" s="52"/>
@@ -49744,7 +49795,7 @@
       </c>
       <c r="B956" s="70"/>
       <c r="C956" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D956" s="52"/>
       <c r="E956" s="52"/>
@@ -49832,7 +49883,7 @@
       <c r="B959" s="70"/>
       <c r="C959" s="73"/>
       <c r="D959" s="52" t="s">
-        <v>272</v>
+        <v>660</v>
       </c>
       <c r="E959" s="52"/>
       <c r="F959" s="52"/>
@@ -49861,7 +49912,7 @@
       <c r="B960" s="70"/>
       <c r="C960" s="73"/>
       <c r="D960" s="52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E960" s="52"/>
       <c r="F960" s="52"/>
@@ -50287,7 +50338,7 @@
         <v>0</v>
       </c>
       <c r="B975" s="68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C975" s="80"/>
       <c r="D975" s="52"/>
@@ -50532,7 +50583,7 @@
         <v>900</v>
       </c>
       <c r="U979" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V979" s="39"/>
       <c r="W979" s="39" t="s">
@@ -50607,7 +50658,7 @@
       <c r="B982" s="70"/>
       <c r="C982" s="73"/>
       <c r="D982" s="52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E982" s="52"/>
       <c r="F982" s="52"/>
@@ -50633,11 +50684,11 @@
     </row>
     <row r="983" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A983" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B983" s="70"/>
       <c r="C983" s="87" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D983" s="52"/>
       <c r="E983" s="52"/>
@@ -50726,7 +50777,7 @@
       </c>
       <c r="B986" s="70"/>
       <c r="C986" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D986" s="52"/>
       <c r="E986" s="52"/>
@@ -50757,7 +50808,7 @@
       </c>
       <c r="B987" s="70"/>
       <c r="C987" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D987" s="52"/>
       <c r="E987" s="52"/>
@@ -50845,7 +50896,7 @@
       <c r="B990" s="70"/>
       <c r="C990" s="73"/>
       <c r="D990" s="78" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E990" s="52"/>
       <c r="F990" s="52"/>
@@ -50874,7 +50925,7 @@
       <c r="B991" s="70"/>
       <c r="C991" s="73"/>
       <c r="D991" s="78" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E991" s="52"/>
       <c r="F991" s="52"/>
@@ -50903,7 +50954,7 @@
       <c r="B992" s="70"/>
       <c r="C992" s="73"/>
       <c r="D992" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E992" s="52"/>
       <c r="F992" s="52"/>
@@ -51329,7 +51380,7 @@
         <v>0</v>
       </c>
       <c r="B1007" s="68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C1007" s="80"/>
       <c r="D1007" s="52"/>
@@ -51462,7 +51513,7 @@
       <c r="B1010" s="69"/>
       <c r="C1010" s="64"/>
       <c r="E1010" s="35" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F1010" s="35">
         <v>18</v>
@@ -51510,7 +51561,7 @@
         <v>930</v>
       </c>
       <c r="U1010" s="35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V1010" s="39"/>
       <c r="W1010" s="39" t="s">
@@ -51583,7 +51634,7 @@
       <c r="B1013" s="70"/>
       <c r="C1013" s="73"/>
       <c r="D1013" s="52" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E1013" s="52"/>
       <c r="F1013" s="52"/>
@@ -51609,11 +51660,11 @@
     </row>
     <row r="1014" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1014" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1014" s="70"/>
       <c r="C1014" s="87" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D1014" s="52"/>
       <c r="E1014" s="52"/>
@@ -51702,7 +51753,7 @@
       </c>
       <c r="B1017" s="70"/>
       <c r="C1017" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1017" s="52"/>
       <c r="E1017" s="52"/>
@@ -51733,7 +51784,7 @@
       </c>
       <c r="B1018" s="70"/>
       <c r="C1018" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1018" s="52"/>
       <c r="E1018" s="52"/>
@@ -51792,7 +51843,7 @@
       <c r="B1020" s="70"/>
       <c r="C1020" s="73"/>
       <c r="D1020" s="78" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E1020" s="52"/>
       <c r="F1020" s="52"/>
@@ -51821,7 +51872,7 @@
       <c r="B1021" s="70"/>
       <c r="C1021" s="73"/>
       <c r="D1021" s="78" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E1021" s="52"/>
       <c r="F1021" s="52"/>
@@ -51850,7 +51901,7 @@
       <c r="B1022" s="70"/>
       <c r="C1022" s="73"/>
       <c r="D1022" s="78" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E1022" s="52"/>
       <c r="F1022" s="52"/>
@@ -52276,7 +52327,7 @@
         <v>0</v>
       </c>
       <c r="B1037" s="68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C1037" s="80"/>
       <c r="D1037" s="52"/>
@@ -52457,7 +52508,7 @@
         <v>930</v>
       </c>
       <c r="U1040" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V1040" s="39"/>
       <c r="W1040" s="39" t="s">
@@ -52473,7 +52524,7 @@
       <c r="B1041" s="69"/>
       <c r="C1041" s="64"/>
       <c r="E1041" s="35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F1041" s="35">
         <v>18</v>
@@ -52585,7 +52636,7 @@
         <v>830</v>
       </c>
       <c r="U1042" s="35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V1042" s="39"/>
       <c r="W1042" s="39" t="s">
@@ -52663,7 +52714,7 @@
       <c r="B1044" s="69"/>
       <c r="C1044" s="64"/>
       <c r="E1044" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F1044" s="35">
         <v>22</v>
@@ -52711,7 +52762,7 @@
         <v>970</v>
       </c>
       <c r="U1044" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="V1044" s="39"/>
       <c r="W1044" s="39" t="s">
@@ -52850,7 +52901,7 @@
       <c r="B1048" s="70"/>
       <c r="C1048" s="73"/>
       <c r="D1048" s="52" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E1048" s="52"/>
       <c r="F1048" s="52"/>
@@ -52876,11 +52927,11 @@
     </row>
     <row r="1049" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1049" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1049" s="70"/>
       <c r="C1049" s="87" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D1049" s="52"/>
       <c r="E1049" s="52"/>
@@ -52969,7 +53020,7 @@
       </c>
       <c r="B1052" s="70"/>
       <c r="C1052" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1052" s="52"/>
       <c r="E1052" s="52"/>
@@ -53000,7 +53051,7 @@
       </c>
       <c r="B1053" s="70"/>
       <c r="C1053" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1053" s="52"/>
       <c r="E1053" s="52"/>
@@ -53059,7 +53110,7 @@
       <c r="B1055" s="70"/>
       <c r="C1055" s="73"/>
       <c r="D1055" s="78" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E1055" s="52"/>
       <c r="F1055" s="52"/>
@@ -53088,7 +53139,7 @@
       <c r="B1056" s="70"/>
       <c r="C1056" s="73"/>
       <c r="D1056" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E1056" s="52"/>
       <c r="F1056" s="52"/>
@@ -53117,7 +53168,7 @@
       <c r="B1057" s="70"/>
       <c r="C1057" s="73"/>
       <c r="D1057" s="78" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E1057" s="52"/>
       <c r="F1057" s="52"/>
@@ -53146,7 +53197,7 @@
       <c r="B1058" s="70"/>
       <c r="C1058" s="73"/>
       <c r="D1058" s="78" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E1058" s="52"/>
       <c r="F1058" s="52"/>
@@ -53572,7 +53623,7 @@
         <v>0</v>
       </c>
       <c r="B1073" s="68" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C1073" s="80"/>
       <c r="D1073" s="52"/>
@@ -54020,7 +54071,7 @@
       <c r="B1082" s="70"/>
       <c r="C1082" s="73"/>
       <c r="D1082" s="52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E1082" s="52"/>
       <c r="F1082" s="52"/>
@@ -54046,11 +54097,11 @@
     </row>
     <row r="1083" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1083" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1083" s="70"/>
       <c r="C1083" s="87" t="s">
-        <v>293</v>
+        <v>661</v>
       </c>
       <c r="D1083" s="52"/>
       <c r="E1083" s="52"/>
@@ -54139,7 +54190,7 @@
       </c>
       <c r="B1086" s="70"/>
       <c r="C1086" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1086" s="52"/>
       <c r="E1086" s="52"/>
@@ -54170,7 +54221,7 @@
       </c>
       <c r="B1087" s="70"/>
       <c r="C1087" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1087" s="52"/>
       <c r="E1087" s="52"/>
@@ -54229,7 +54280,7 @@
       <c r="B1089" s="70"/>
       <c r="C1089" s="73"/>
       <c r="D1089" s="78" t="s">
-        <v>559</v>
+        <v>662</v>
       </c>
       <c r="E1089" s="52"/>
       <c r="F1089" s="52"/>
@@ -54258,7 +54309,7 @@
       <c r="B1090" s="70"/>
       <c r="C1090" s="73"/>
       <c r="D1090" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E1090" s="52"/>
       <c r="F1090" s="52"/>
@@ -54287,7 +54338,7 @@
       <c r="B1091" s="70"/>
       <c r="C1091" s="73"/>
       <c r="D1091" s="78" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E1091" s="52"/>
       <c r="F1091" s="52"/>
@@ -54713,7 +54764,7 @@
         <v>0</v>
       </c>
       <c r="B1106" s="68" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C1106" s="80"/>
       <c r="D1106" s="52"/>
@@ -54846,7 +54897,7 @@
       <c r="B1109" s="69"/>
       <c r="C1109" s="64"/>
       <c r="E1109" s="35" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F1109" s="35">
         <v>16</v>
@@ -55161,7 +55212,7 @@
       <c r="B1115" s="70"/>
       <c r="C1115" s="73"/>
       <c r="D1115" s="52" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E1115" s="52"/>
       <c r="F1115" s="52"/>
@@ -55187,11 +55238,11 @@
     </row>
     <row r="1116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1116" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1116" s="70"/>
       <c r="C1116" s="87" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D1116" s="52"/>
       <c r="E1116" s="52"/>
@@ -55280,7 +55331,7 @@
       </c>
       <c r="B1119" s="70"/>
       <c r="C1119" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1119" s="52"/>
       <c r="E1119" s="52"/>
@@ -55311,7 +55362,7 @@
       </c>
       <c r="B1120" s="70"/>
       <c r="C1120" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1120" s="52"/>
       <c r="E1120" s="52"/>
@@ -55370,7 +55421,7 @@
       <c r="B1122" s="70"/>
       <c r="C1122" s="73"/>
       <c r="D1122" s="78" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E1122" s="52"/>
       <c r="F1122" s="52"/>
@@ -55399,7 +55450,7 @@
       <c r="B1123" s="70"/>
       <c r="C1123" s="73"/>
       <c r="D1123" s="78" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E1123" s="52"/>
       <c r="F1123" s="52"/>
@@ -55428,7 +55479,7 @@
       <c r="B1124" s="70"/>
       <c r="C1124" s="73"/>
       <c r="D1124" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E1124" s="52"/>
       <c r="F1124" s="52"/>
@@ -55854,7 +55905,7 @@
         <v>0</v>
       </c>
       <c r="B1139" s="68" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C1139" s="80"/>
       <c r="D1139" s="52"/>
@@ -56099,7 +56150,7 @@
         <v>900</v>
       </c>
       <c r="U1143" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V1143" s="39"/>
       <c r="W1143" s="39" t="s">
@@ -56174,7 +56225,7 @@
       <c r="B1146" s="70"/>
       <c r="C1146" s="73"/>
       <c r="D1146" s="52" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E1146" s="52"/>
       <c r="F1146" s="52"/>
@@ -56200,11 +56251,11 @@
     </row>
     <row r="1147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1147" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1147" s="70"/>
       <c r="C1147" s="87" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D1147" s="52"/>
       <c r="E1147" s="52"/>
@@ -56293,7 +56344,7 @@
       </c>
       <c r="B1150" s="70"/>
       <c r="C1150" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1150" s="52"/>
       <c r="E1150" s="52"/>
@@ -56324,7 +56375,7 @@
       </c>
       <c r="B1151" s="70"/>
       <c r="C1151" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1151" s="52"/>
       <c r="E1151" s="52"/>
@@ -56383,7 +56434,7 @@
       <c r="B1153" s="70"/>
       <c r="C1153" s="73"/>
       <c r="D1153" s="78" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E1153" s="52"/>
       <c r="F1153" s="52"/>
@@ -56412,7 +56463,7 @@
       <c r="B1154" s="70"/>
       <c r="C1154" s="73"/>
       <c r="D1154" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E1154" s="52"/>
       <c r="F1154" s="52"/>
@@ -56441,7 +56492,7 @@
       <c r="B1155" s="70"/>
       <c r="C1155" s="73"/>
       <c r="D1155" s="78" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E1155" s="52"/>
       <c r="F1155" s="52"/>
@@ -56470,7 +56521,7 @@
       <c r="B1156" s="70"/>
       <c r="C1156" s="73"/>
       <c r="D1156" s="78" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E1156" s="52"/>
       <c r="F1156" s="52"/>
@@ -56896,7 +56947,7 @@
         <v>0</v>
       </c>
       <c r="B1171" s="68" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C1171" s="80"/>
       <c r="D1171" s="52"/>
@@ -57212,7 +57263,7 @@
       <c r="B1178" s="70"/>
       <c r="C1178" s="73"/>
       <c r="D1178" s="52" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E1178" s="52"/>
       <c r="F1178" s="52"/>
@@ -57238,11 +57289,11 @@
     </row>
     <row r="1179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1179" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1179" s="70"/>
       <c r="C1179" s="87" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D1179" s="52"/>
       <c r="E1179" s="52"/>
@@ -57331,7 +57382,7 @@
       </c>
       <c r="B1182" s="70"/>
       <c r="C1182" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1182" s="52"/>
       <c r="E1182" s="52"/>
@@ -57362,7 +57413,7 @@
       </c>
       <c r="B1183" s="70"/>
       <c r="C1183" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1183" s="52"/>
       <c r="E1183" s="52"/>
@@ -57421,7 +57472,7 @@
       <c r="B1185" s="70"/>
       <c r="C1185" s="73"/>
       <c r="D1185" s="78" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E1185" s="52"/>
       <c r="F1185" s="52"/>
@@ -57450,7 +57501,7 @@
       <c r="B1186" s="70"/>
       <c r="C1186" s="73"/>
       <c r="D1186" s="78" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E1186" s="52"/>
       <c r="F1186" s="52"/>
@@ -57479,7 +57530,7 @@
       <c r="B1187" s="70"/>
       <c r="C1187" s="73"/>
       <c r="D1187" s="78" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E1187" s="52"/>
       <c r="F1187" s="52"/>
@@ -57905,7 +57956,7 @@
         <v>0</v>
       </c>
       <c r="B1202" s="68" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C1202" s="80"/>
       <c r="D1202" s="52"/>
@@ -58206,7 +58257,7 @@
         <v>900</v>
       </c>
       <c r="U1207" s="35" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V1207" s="39"/>
       <c r="W1207" s="39"/>
@@ -58277,7 +58328,7 @@
       <c r="B1210" s="70"/>
       <c r="C1210" s="73"/>
       <c r="D1210" s="52" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E1210" s="52"/>
       <c r="F1210" s="52"/>
@@ -58303,11 +58354,11 @@
     </row>
     <row r="1211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1211" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1211" s="70"/>
       <c r="C1211" s="87" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D1211" s="52"/>
       <c r="E1211" s="52"/>
@@ -58396,7 +58447,7 @@
       </c>
       <c r="B1214" s="70"/>
       <c r="C1214" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1214" s="52"/>
       <c r="E1214" s="52"/>
@@ -58427,7 +58478,7 @@
       </c>
       <c r="B1215" s="70"/>
       <c r="C1215" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1215" s="52"/>
       <c r="E1215" s="52"/>
@@ -58486,7 +58537,7 @@
       <c r="B1217" s="70"/>
       <c r="C1217" s="73"/>
       <c r="D1217" s="78" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E1217" s="52"/>
       <c r="F1217" s="52"/>
@@ -58515,7 +58566,7 @@
       <c r="B1218" s="70"/>
       <c r="C1218" s="73"/>
       <c r="D1218" s="78" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E1218" s="52"/>
       <c r="F1218" s="52"/>
@@ -58544,7 +58595,7 @@
       <c r="B1219" s="70"/>
       <c r="C1219" s="73"/>
       <c r="D1219" s="78" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E1219" s="52"/>
       <c r="F1219" s="52"/>
@@ -58573,7 +58624,7 @@
       <c r="B1220" s="70"/>
       <c r="C1220" s="73"/>
       <c r="D1220" s="78" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E1220" s="52"/>
       <c r="F1220" s="52"/>
@@ -58999,7 +59050,7 @@
         <v>0</v>
       </c>
       <c r="B1235" s="144" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C1235" s="145"/>
       <c r="D1235" s="52"/>
@@ -59379,7 +59430,7 @@
       <c r="B1243" s="70"/>
       <c r="C1243" s="73"/>
       <c r="D1243" s="52" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E1243" s="52"/>
       <c r="F1243" s="52"/>
@@ -59405,11 +59456,11 @@
     </row>
     <row r="1244" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1244" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1244" s="70"/>
       <c r="C1244" s="87" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D1244" s="52"/>
       <c r="E1244" s="52"/>
@@ -59583,7 +59634,7 @@
       <c r="B1250" s="70"/>
       <c r="C1250" s="73"/>
       <c r="D1250" s="78" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E1250" s="52"/>
       <c r="F1250" s="52"/>
@@ -59612,7 +59663,7 @@
       <c r="B1251" s="70"/>
       <c r="C1251" s="73"/>
       <c r="D1251" s="78" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E1251" s="52"/>
       <c r="F1251" s="52"/>
@@ -59641,7 +59692,7 @@
       <c r="B1252" s="70"/>
       <c r="C1252" s="73"/>
       <c r="D1252" s="78" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E1252" s="52"/>
       <c r="F1252" s="52"/>
@@ -59670,7 +59721,7 @@
       <c r="B1253" s="70"/>
       <c r="C1253" s="73"/>
       <c r="D1253" s="78" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E1253" s="52"/>
       <c r="F1253" s="52"/>
@@ -60096,7 +60147,7 @@
         <v>0</v>
       </c>
       <c r="B1268" s="68" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C1268" s="80"/>
       <c r="D1268" s="52"/>
@@ -60277,7 +60328,7 @@
         <v>830</v>
       </c>
       <c r="U1271" s="35" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="V1271" s="39"/>
       <c r="W1271" s="39" t="s">
@@ -60341,7 +60392,7 @@
         <v>830</v>
       </c>
       <c r="U1272" s="35" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="V1272" s="39"/>
       <c r="W1272" s="39" t="s">
@@ -60405,7 +60456,7 @@
         <v>900</v>
       </c>
       <c r="U1273" s="35" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="V1273" s="39"/>
       <c r="W1273" s="39" t="s">
@@ -60449,7 +60500,7 @@
       <c r="B1275" s="70"/>
       <c r="C1275" s="73"/>
       <c r="D1275" s="52" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E1275" s="52"/>
       <c r="F1275" s="52"/>
@@ -60480,7 +60531,7 @@
       <c r="B1276" s="70"/>
       <c r="C1276" s="73"/>
       <c r="D1276" s="52" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E1276" s="52"/>
       <c r="F1276" s="52"/>
@@ -60506,11 +60557,11 @@
     </row>
     <row r="1277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1277" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1277" s="70"/>
       <c r="C1277" s="87" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D1277" s="52"/>
       <c r="E1277" s="52"/>
@@ -60599,7 +60650,7 @@
       </c>
       <c r="B1280" s="70"/>
       <c r="C1280" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1280" s="52"/>
       <c r="E1280" s="52"/>
@@ -60630,7 +60681,7 @@
       </c>
       <c r="B1281" s="70"/>
       <c r="C1281" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1281" s="52"/>
       <c r="E1281" s="52"/>
@@ -60689,7 +60740,7 @@
       <c r="B1283" s="70"/>
       <c r="C1283" s="73"/>
       <c r="D1283" s="78" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E1283" s="52"/>
       <c r="F1283" s="52"/>
@@ -60718,7 +60769,7 @@
       <c r="B1284" s="70"/>
       <c r="C1284" s="73"/>
       <c r="D1284" s="78" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E1284" s="52"/>
       <c r="F1284" s="52"/>
@@ -60747,7 +60798,7 @@
       <c r="B1285" s="70"/>
       <c r="C1285" s="73"/>
       <c r="D1285" s="78" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="E1285" s="52"/>
       <c r="F1285" s="52"/>
@@ -60776,7 +60827,7 @@
       <c r="B1286" s="70"/>
       <c r="C1286" s="73"/>
       <c r="D1286" s="78" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="E1286" s="52"/>
       <c r="F1286" s="52"/>
@@ -60805,7 +60856,7 @@
       <c r="B1287" s="70"/>
       <c r="C1287" s="73"/>
       <c r="D1287" s="78" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E1287" s="52"/>
       <c r="F1287" s="52"/>
@@ -61231,7 +61282,7 @@
         <v>0</v>
       </c>
       <c r="B1302" s="68" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C1302" s="80"/>
       <c r="D1302" s="52"/>
@@ -61364,7 +61415,7 @@
       <c r="B1305" s="69"/>
       <c r="C1305" s="64"/>
       <c r="E1305" s="35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F1305" s="35">
         <v>18</v>
@@ -61412,7 +61463,7 @@
         <v>930</v>
       </c>
       <c r="U1305" s="35" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="V1305" s="39"/>
       <c r="W1305" s="39" t="s">
@@ -61554,7 +61605,7 @@
       <c r="B1308" s="69"/>
       <c r="C1308" s="64"/>
       <c r="E1308" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F1308" s="35">
         <v>18</v>
@@ -61602,7 +61653,7 @@
         <v>830</v>
       </c>
       <c r="U1308" s="35" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="V1308" s="39"/>
       <c r="W1308" s="39" t="s">
@@ -61618,7 +61669,7 @@
       <c r="B1309" s="69"/>
       <c r="C1309" s="64"/>
       <c r="E1309" s="35" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F1309" s="35">
         <v>20</v>
@@ -61666,7 +61717,7 @@
         <v>900</v>
       </c>
       <c r="U1309" s="35" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="V1309" s="39"/>
       <c r="W1309" s="39" t="s">
@@ -61794,7 +61845,7 @@
         <v>830</v>
       </c>
       <c r="U1311" s="35" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="V1311" s="39"/>
       <c r="W1311" s="39" t="s">
@@ -61858,7 +61909,7 @@
         <v>900</v>
       </c>
       <c r="U1312" s="35" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="V1312" s="39"/>
       <c r="W1312" s="39" t="s">
@@ -61922,7 +61973,7 @@
         <v>830</v>
       </c>
       <c r="U1313" s="35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V1313" s="39"/>
       <c r="W1313" s="39" t="s">
@@ -61986,7 +62037,7 @@
         <v>900</v>
       </c>
       <c r="U1314" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V1314" s="39"/>
       <c r="W1314" s="39" t="s">
@@ -62030,7 +62081,7 @@
       <c r="B1316" s="70"/>
       <c r="C1316" s="73"/>
       <c r="D1316" s="52" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E1316" s="52"/>
       <c r="F1316" s="52"/>
@@ -62061,7 +62112,7 @@
       <c r="B1317" s="70"/>
       <c r="C1317" s="73"/>
       <c r="D1317" s="52" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E1317" s="52"/>
       <c r="F1317" s="52"/>
@@ -62087,11 +62138,11 @@
     </row>
     <row r="1318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1318" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1318" s="70"/>
       <c r="C1318" s="87" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D1318" s="52"/>
       <c r="E1318" s="52"/>
@@ -62180,7 +62231,7 @@
       </c>
       <c r="B1321" s="70"/>
       <c r="C1321" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1321" s="52"/>
       <c r="E1321" s="52"/>
@@ -62211,7 +62262,7 @@
       </c>
       <c r="B1322" s="70"/>
       <c r="C1322" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1322" s="52"/>
       <c r="E1322" s="52"/>
@@ -62270,7 +62321,7 @@
       <c r="B1324" s="70"/>
       <c r="C1324" s="73"/>
       <c r="D1324" s="78" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E1324" s="52"/>
       <c r="F1324" s="52"/>
@@ -62299,7 +62350,7 @@
       <c r="B1325" s="70"/>
       <c r="C1325" s="73"/>
       <c r="D1325" s="78" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E1325" s="52"/>
       <c r="F1325" s="52"/>
@@ -62328,7 +62379,7 @@
       <c r="B1326" s="70"/>
       <c r="C1326" s="73"/>
       <c r="D1326" s="78" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E1326" s="52"/>
       <c r="F1326" s="52"/>
@@ -62357,7 +62408,7 @@
       <c r="B1327" s="70"/>
       <c r="C1327" s="73"/>
       <c r="D1327" s="78" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E1327" s="52"/>
       <c r="F1327" s="52"/>
@@ -62783,7 +62834,7 @@
         <v>0</v>
       </c>
       <c r="B1342" s="68" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C1342" s="80"/>
       <c r="D1342" s="52"/>
@@ -62964,7 +63015,7 @@
         <v>830</v>
       </c>
       <c r="U1345" s="98" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="V1345" s="103"/>
       <c r="W1345" s="103" t="s">
@@ -63028,7 +63079,7 @@
         <v>930</v>
       </c>
       <c r="U1346" s="98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V1346" s="103"/>
       <c r="W1346" s="103" t="s">
@@ -63044,7 +63095,7 @@
       <c r="B1347" s="69"/>
       <c r="C1347" s="64"/>
       <c r="E1347" s="98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F1347" s="98">
         <v>18</v>
@@ -63092,7 +63143,7 @@
         <v>930</v>
       </c>
       <c r="U1347" s="98" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="V1347" s="103"/>
       <c r="W1347" s="103" t="s">
@@ -63108,7 +63159,7 @@
       <c r="B1348" s="69"/>
       <c r="C1348" s="64"/>
       <c r="E1348" s="98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F1348" s="98">
         <v>16</v>
@@ -63296,7 +63347,7 @@
       <c r="B1351" s="69"/>
       <c r="C1351" s="64"/>
       <c r="E1351" s="106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F1351" s="106">
         <v>18</v>
@@ -63344,7 +63395,7 @@
         <v>830</v>
       </c>
       <c r="U1351" s="106" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="V1351" s="110"/>
       <c r="W1351" s="141" t="s">
@@ -63358,7 +63409,7 @@
       <c r="B1352" s="69"/>
       <c r="C1352" s="64"/>
       <c r="E1352" s="98" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F1352" s="98">
         <v>20</v>
@@ -63406,7 +63457,7 @@
         <v>900</v>
       </c>
       <c r="U1352" s="98" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="V1352" s="103"/>
       <c r="W1352" s="103" t="s">
@@ -63486,7 +63537,7 @@
       <c r="B1354" s="69"/>
       <c r="C1354" s="64"/>
       <c r="E1354" s="98" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F1354" s="98">
         <v>18</v>
@@ -63534,7 +63585,7 @@
         <v>930</v>
       </c>
       <c r="U1354" s="98" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="V1354" s="103"/>
       <c r="W1354" s="120"/>
@@ -63594,7 +63645,7 @@
         <v>900</v>
       </c>
       <c r="U1355" s="98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V1355" s="103"/>
       <c r="W1355" s="103" t="s">
@@ -63658,7 +63709,7 @@
         <v>900</v>
       </c>
       <c r="U1356" s="98" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="V1356" s="103"/>
       <c r="W1356" s="103" t="s">
@@ -63720,7 +63771,7 @@
         <v>900</v>
       </c>
       <c r="U1357" s="98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="V1357" s="103"/>
       <c r="W1357" s="103" t="s">
@@ -63764,7 +63815,7 @@
       <c r="B1359" s="70"/>
       <c r="C1359" s="73"/>
       <c r="D1359" s="52" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E1359" s="52"/>
       <c r="F1359" s="52"/>
@@ -63795,7 +63846,7 @@
       <c r="B1360" s="70"/>
       <c r="C1360" s="73"/>
       <c r="D1360" s="52" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E1360" s="52"/>
       <c r="F1360" s="52"/>
@@ -63821,11 +63872,11 @@
     </row>
     <row r="1361" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1361" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1361" s="70"/>
       <c r="C1361" s="87" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D1361" s="52"/>
       <c r="E1361" s="52"/>
@@ -63914,7 +63965,7 @@
       </c>
       <c r="B1364" s="70"/>
       <c r="C1364" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1364" s="52"/>
       <c r="E1364" s="52"/>
@@ -63945,7 +63996,7 @@
       </c>
       <c r="B1365" s="70"/>
       <c r="C1365" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1365" s="52"/>
       <c r="E1365" s="52"/>
@@ -64004,7 +64055,7 @@
       <c r="B1367" s="70"/>
       <c r="C1367" s="73"/>
       <c r="D1367" s="78" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E1367" s="52"/>
       <c r="F1367" s="52"/>
@@ -64033,7 +64084,7 @@
       <c r="B1368" s="70"/>
       <c r="C1368" s="73"/>
       <c r="D1368" s="78" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E1368" s="52"/>
       <c r="F1368" s="52"/>
@@ -64459,7 +64510,7 @@
         <v>0</v>
       </c>
       <c r="B1383" s="143" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C1383" s="80"/>
       <c r="D1383" s="52"/>
@@ -64720,7 +64771,7 @@
       <c r="B1388" s="69"/>
       <c r="C1388" s="64"/>
       <c r="E1388" s="106" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F1388" s="106">
         <v>20</v>
@@ -64760,7 +64811,7 @@
       <c r="S1388" s="106"/>
       <c r="T1388" s="106"/>
       <c r="U1388" s="106" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="V1388" s="110"/>
       <c r="W1388" s="110" t="s">
@@ -64970,7 +65021,7 @@
       <c r="B1393" s="70"/>
       <c r="C1393" s="73"/>
       <c r="D1393" s="52" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E1393" s="52"/>
       <c r="F1393" s="52"/>
@@ -65001,7 +65052,7 @@
       <c r="B1394" s="70"/>
       <c r="C1394" s="73"/>
       <c r="D1394" s="52" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E1394" s="52"/>
       <c r="F1394" s="52"/>
@@ -65027,11 +65078,11 @@
     </row>
     <row r="1395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1395" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1395" s="70"/>
       <c r="C1395" s="87" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D1395" s="52"/>
       <c r="E1395" s="52"/>
@@ -65120,7 +65171,7 @@
       </c>
       <c r="B1398" s="70"/>
       <c r="C1398" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1398" s="52"/>
       <c r="E1398" s="52"/>
@@ -65151,7 +65202,7 @@
       </c>
       <c r="B1399" s="70"/>
       <c r="C1399" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1399" s="52"/>
       <c r="E1399" s="52"/>
@@ -65210,7 +65261,7 @@
       <c r="B1401" s="70"/>
       <c r="C1401" s="73"/>
       <c r="D1401" s="52" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E1401" s="52"/>
       <c r="F1401" s="52"/>
@@ -65238,7 +65289,7 @@
       <c r="B1402" s="70"/>
       <c r="C1402" s="73"/>
       <c r="D1402" s="78" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E1402" s="52"/>
       <c r="F1402" s="52"/>
@@ -65267,7 +65318,7 @@
       <c r="B1403" s="70"/>
       <c r="C1403" s="73"/>
       <c r="D1403" s="78" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E1403" s="52"/>
       <c r="F1403" s="52"/>
@@ -65693,7 +65744,7 @@
         <v>0</v>
       </c>
       <c r="B1418" s="68" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C1418" s="80"/>
       <c r="D1418" s="52"/>
@@ -65874,7 +65925,7 @@
         <v>930</v>
       </c>
       <c r="U1421" s="35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="V1421" s="39"/>
       <c r="W1421" s="39"/>
@@ -65934,7 +65985,7 @@
         <v>830</v>
       </c>
       <c r="U1422" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="V1422" s="39"/>
       <c r="W1422" s="39"/>
@@ -65946,7 +65997,7 @@
       <c r="B1423" s="69"/>
       <c r="C1423" s="64"/>
       <c r="E1423" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F1423" s="35">
         <v>20</v>
@@ -65994,7 +66045,7 @@
         <v>900</v>
       </c>
       <c r="U1423" s="35" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="V1423" s="39"/>
       <c r="W1423" s="39"/>
@@ -66006,7 +66057,7 @@
       <c r="B1424" s="69"/>
       <c r="C1424" s="64"/>
       <c r="E1424" s="35" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F1424" s="35">
         <v>20</v>
@@ -66054,7 +66105,7 @@
         <v>900</v>
       </c>
       <c r="U1424" s="35" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="V1424" s="39"/>
       <c r="W1424" s="39"/>
@@ -66114,7 +66165,7 @@
         <v>930</v>
       </c>
       <c r="U1425" s="35" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="V1425" s="39"/>
       <c r="W1425" s="39"/>
@@ -66174,7 +66225,7 @@
         <v>830</v>
       </c>
       <c r="U1426" s="35" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="V1426" s="39"/>
       <c r="W1426" s="39"/>
@@ -66214,7 +66265,7 @@
       <c r="B1428" s="70"/>
       <c r="C1428" s="73"/>
       <c r="D1428" s="52" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E1428" s="52"/>
       <c r="F1428" s="52"/>
@@ -66245,7 +66296,7 @@
       <c r="B1429" s="70"/>
       <c r="C1429" s="73"/>
       <c r="D1429" s="52" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E1429" s="52"/>
       <c r="F1429" s="52"/>
@@ -66271,11 +66322,11 @@
     </row>
     <row r="1430" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1430" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1430" s="70"/>
       <c r="C1430" s="87" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D1430" s="52"/>
       <c r="E1430" s="52"/>
@@ -66334,7 +66385,7 @@
       <c r="B1432" s="70"/>
       <c r="C1432" s="80"/>
       <c r="D1432" s="52" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E1432" s="52"/>
       <c r="F1432" s="52"/>
@@ -66364,7 +66415,7 @@
       </c>
       <c r="B1433" s="70"/>
       <c r="C1433" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1433" s="52"/>
       <c r="E1433" s="52"/>
@@ -66395,7 +66446,7 @@
       </c>
       <c r="B1434" s="70"/>
       <c r="C1434" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1434" s="52"/>
       <c r="E1434" s="52"/>
@@ -66454,7 +66505,7 @@
       <c r="B1436" s="70"/>
       <c r="C1436" s="73"/>
       <c r="D1436" s="78" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E1436" s="52"/>
       <c r="F1436" s="52"/>
@@ -66483,7 +66534,7 @@
       <c r="B1437" s="70"/>
       <c r="C1437" s="73"/>
       <c r="D1437" s="78" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E1437" s="52"/>
       <c r="F1437" s="52"/>
@@ -66512,7 +66563,7 @@
       <c r="B1438" s="70"/>
       <c r="C1438" s="73"/>
       <c r="D1438" s="78" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E1438" s="52"/>
       <c r="F1438" s="52"/>
@@ -66938,7 +66989,7 @@
         <v>0</v>
       </c>
       <c r="B1453" s="68" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C1453" s="80"/>
       <c r="D1453" s="52"/>
@@ -67119,11 +67170,11 @@
         <v>830</v>
       </c>
       <c r="U1456" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="V1456" s="39"/>
       <c r="W1456" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="X1456" s="39"/>
       <c r="Y1456" s="52"/>
@@ -67181,11 +67232,11 @@
         <v>830</v>
       </c>
       <c r="U1457" s="35" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="V1457" s="39"/>
       <c r="W1457" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="X1457" s="39"/>
       <c r="Y1457" s="52"/>
@@ -67223,7 +67274,7 @@
       <c r="B1459" s="70"/>
       <c r="C1459" s="73"/>
       <c r="D1459" s="52" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E1459" s="52"/>
       <c r="F1459" s="52"/>
@@ -67254,7 +67305,7 @@
       <c r="B1460" s="70"/>
       <c r="C1460" s="73"/>
       <c r="D1460" s="52" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E1460" s="52"/>
       <c r="F1460" s="52"/>
@@ -67280,11 +67331,11 @@
     </row>
     <row r="1461" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1461" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1461" s="70"/>
       <c r="C1461" s="87" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D1461" s="52"/>
       <c r="E1461" s="52"/>
@@ -67343,7 +67394,7 @@
       <c r="B1463" s="70"/>
       <c r="C1463" s="80"/>
       <c r="D1463" s="52" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E1463" s="52"/>
       <c r="F1463" s="52"/>
@@ -67373,7 +67424,7 @@
       </c>
       <c r="B1464" s="70"/>
       <c r="C1464" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1464" s="52"/>
       <c r="E1464" s="52"/>
@@ -67404,7 +67455,7 @@
       </c>
       <c r="B1465" s="70"/>
       <c r="C1465" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1465" s="52"/>
       <c r="E1465" s="52"/>
@@ -67463,7 +67514,7 @@
       <c r="B1467" s="70"/>
       <c r="C1467" s="73"/>
       <c r="D1467" s="78" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E1467" s="52"/>
       <c r="F1467" s="52"/>
@@ -67492,7 +67543,7 @@
       <c r="B1468" s="70"/>
       <c r="C1468" s="73"/>
       <c r="D1468" s="78" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E1468" s="52"/>
       <c r="F1468" s="52"/>
@@ -67521,7 +67572,7 @@
       <c r="B1469" s="70"/>
       <c r="C1469" s="73"/>
       <c r="D1469" s="78" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E1469" s="52"/>
       <c r="F1469" s="52"/>
@@ -67550,7 +67601,7 @@
       <c r="B1470" s="70"/>
       <c r="C1470" s="73"/>
       <c r="D1470" s="78" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E1470" s="52"/>
       <c r="F1470" s="52"/>
@@ -67976,7 +68027,7 @@
         <v>0</v>
       </c>
       <c r="B1485" s="68" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C1485" s="80"/>
       <c r="D1485" s="52"/>
@@ -68221,7 +68272,7 @@
         <v>830</v>
       </c>
       <c r="U1489" s="35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V1489" s="39"/>
       <c r="W1489" s="39" t="s">
@@ -68285,7 +68336,7 @@
         <v>900</v>
       </c>
       <c r="U1490" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V1490" s="39"/>
       <c r="W1490" s="39" t="s">
@@ -68329,7 +68380,7 @@
       <c r="B1492" s="70"/>
       <c r="C1492" s="73"/>
       <c r="D1492" s="52" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E1492" s="52"/>
       <c r="F1492" s="52"/>
@@ -68360,7 +68411,7 @@
       <c r="B1493" s="70"/>
       <c r="C1493" s="73"/>
       <c r="D1493" s="52" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E1493" s="52"/>
       <c r="F1493" s="52"/>
@@ -68386,11 +68437,11 @@
     </row>
     <row r="1494" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1494" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1494" s="70"/>
       <c r="C1494" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D1494" s="52"/>
       <c r="E1494" s="52"/>
@@ -68479,7 +68530,7 @@
       </c>
       <c r="B1497" s="70"/>
       <c r="C1497" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1497" s="52"/>
       <c r="E1497" s="52"/>
@@ -68510,7 +68561,7 @@
       </c>
       <c r="B1498" s="70"/>
       <c r="C1498" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1498" s="52"/>
       <c r="E1498" s="52"/>
@@ -68569,7 +68620,7 @@
       <c r="B1500" s="70"/>
       <c r="C1500" s="73"/>
       <c r="D1500" s="78" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="E1500" s="52"/>
       <c r="F1500" s="52"/>
@@ -68598,7 +68649,7 @@
       <c r="B1501" s="70"/>
       <c r="C1501" s="73"/>
       <c r="D1501" s="78" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E1501" s="52"/>
       <c r="F1501" s="52"/>
@@ -68627,7 +68678,7 @@
       <c r="B1502" s="70"/>
       <c r="C1502" s="73"/>
       <c r="D1502" s="78" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E1502" s="52"/>
       <c r="F1502" s="52"/>
@@ -68656,7 +68707,7 @@
       <c r="B1503" s="70"/>
       <c r="C1503" s="73"/>
       <c r="D1503" s="78" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E1503" s="52"/>
       <c r="F1503" s="52"/>
@@ -69082,7 +69133,7 @@
         <v>0</v>
       </c>
       <c r="B1518" s="68" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C1518" s="80"/>
       <c r="D1518" s="52"/>
@@ -69371,7 +69422,7 @@
       <c r="B1524" s="70"/>
       <c r="C1524" s="73"/>
       <c r="D1524" s="52" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E1524" s="52"/>
       <c r="F1524" s="52"/>
@@ -69402,7 +69453,7 @@
       <c r="B1525" s="70"/>
       <c r="C1525" s="73"/>
       <c r="D1525" s="52" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E1525" s="52"/>
       <c r="F1525" s="52"/>
@@ -69428,11 +69479,11 @@
     </row>
     <row r="1526" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1526" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1526" s="70"/>
       <c r="C1526" s="87" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D1526" s="52"/>
       <c r="E1526" s="52"/>
@@ -69521,7 +69572,7 @@
       </c>
       <c r="B1529" s="70"/>
       <c r="C1529" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1529" s="52"/>
       <c r="E1529" s="52"/>
@@ -69552,7 +69603,7 @@
       </c>
       <c r="B1530" s="70"/>
       <c r="C1530" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1530" s="52"/>
       <c r="E1530" s="52"/>
@@ -69611,7 +69662,7 @@
       <c r="B1532" s="70"/>
       <c r="C1532" s="73"/>
       <c r="D1532" s="78" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E1532" s="52"/>
       <c r="F1532" s="52"/>
@@ -69640,7 +69691,7 @@
       <c r="B1533" s="70"/>
       <c r="C1533" s="73"/>
       <c r="D1533" s="78" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E1533" s="52"/>
       <c r="F1533" s="52"/>
@@ -69669,7 +69720,7 @@
       <c r="B1534" s="70"/>
       <c r="C1534" s="73"/>
       <c r="D1534" s="78" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E1534" s="52"/>
       <c r="F1534" s="52"/>
@@ -69698,7 +69749,7 @@
       <c r="B1535" s="70"/>
       <c r="C1535" s="73"/>
       <c r="D1535" s="78" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E1535" s="52"/>
       <c r="F1535" s="52"/>
@@ -70124,7 +70175,7 @@
         <v>0</v>
       </c>
       <c r="B1550" s="68" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C1550" s="80"/>
       <c r="D1550" s="52"/>
@@ -70413,7 +70464,7 @@
       <c r="B1556" s="70"/>
       <c r="C1556" s="73"/>
       <c r="D1556" s="52" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E1556" s="52"/>
       <c r="F1556" s="52"/>
@@ -70444,7 +70495,7 @@
       <c r="B1557" s="70"/>
       <c r="C1557" s="73"/>
       <c r="D1557" s="52" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E1557" s="52"/>
       <c r="F1557" s="52"/>
@@ -70470,11 +70521,11 @@
     </row>
     <row r="1558" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1558" s="29" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B1558" s="70"/>
       <c r="C1558" s="87" t="s">
-        <v>346</v>
+        <v>663</v>
       </c>
       <c r="D1558" s="52"/>
       <c r="E1558" s="52"/>
@@ -70563,7 +70614,7 @@
       </c>
       <c r="B1561" s="70"/>
       <c r="C1561" s="87" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1561" s="52"/>
       <c r="E1561" s="52"/>
@@ -70594,7 +70645,7 @@
       </c>
       <c r="B1562" s="70"/>
       <c r="C1562" s="87" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D1562" s="52"/>
       <c r="E1562" s="52"/>
@@ -70653,7 +70704,7 @@
       <c r="B1564" s="70"/>
       <c r="C1564" s="73"/>
       <c r="D1564" s="78" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E1564" s="52"/>
       <c r="F1564" s="52"/>
@@ -70682,7 +70733,7 @@
       <c r="B1565" s="70"/>
       <c r="C1565" s="73"/>
       <c r="D1565" s="78" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E1565" s="52"/>
       <c r="F1565" s="52"/>
@@ -70711,7 +70762,7 @@
       <c r="B1566" s="70"/>
       <c r="C1566" s="73"/>
       <c r="D1566" s="78" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E1566" s="52"/>
       <c r="F1566" s="52"/>
@@ -70740,7 +70791,7 @@
       <c r="B1567" s="70"/>
       <c r="C1567" s="73"/>
       <c r="D1567" s="78" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E1567" s="52"/>
       <c r="F1567" s="52"/>

--- a/Aeolus-Wireframe-06.xlsx
+++ b/Aeolus-Wireframe-06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cld\Aeolus-Tire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECC380A-6CB4-4314-A311-14226883891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5851CE78-194A-4F28-BEAE-842112E97F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30720" yWindow="552" windowWidth="23040" windowHeight="13740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18936" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Support" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4459" uniqueCount="661">
   <si>
     <t>Tire Name</t>
   </si>
@@ -2024,15 +2024,6 @@
     <t>The new dual-layer tread structure uses a medium- and long-distance compound formulation to balance mileage and heat dissipation, maintaining durability and performance even under heavy-duty operations.</t>
   </si>
   <si>
-    <t>ai rec' 12.2</t>
-  </si>
-  <si>
-    <t>ai rec' 11.6</t>
-  </si>
-  <si>
-    <t>ai rec' 11.7</t>
-  </si>
-  <si>
     <t>Designed for use on “Last mile” Delivery Vehicle</t>
   </si>
   <si>
@@ -2240,7 +2231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2310,12 +2301,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2403,7 +2388,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -2840,12 +2825,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -20357,9 +20338,7 @@
       <c r="Y105" s="52"/>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A106" s="158" t="s">
-        <v>659</v>
-      </c>
+      <c r="A106" s="52"/>
       <c r="B106" s="69"/>
       <c r="C106" s="64"/>
       <c r="E106" s="35" t="s">
@@ -20371,8 +20350,8 @@
       <c r="G106" s="36">
         <v>9</v>
       </c>
-      <c r="H106" s="157">
-        <v>297</v>
+      <c r="H106" s="156">
+        <v>11.7</v>
       </c>
       <c r="I106" s="37">
         <v>40.4</v>
@@ -24836,9 +24815,7 @@
       <c r="Y243" s="52"/>
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A244" s="158" t="s">
-        <v>658</v>
-      </c>
+      <c r="A244" s="52"/>
       <c r="B244" s="69"/>
       <c r="C244" s="64"/>
       <c r="E244" s="35" t="s">
@@ -24850,8 +24827,8 @@
       <c r="G244" s="36">
         <v>9</v>
       </c>
-      <c r="H244" s="157">
-        <v>296</v>
+      <c r="H244" s="156">
+        <v>11.7</v>
       </c>
       <c r="I244" s="37">
         <v>39.9</v>
@@ -26018,9 +25995,7 @@
       <c r="Y278" s="52"/>
     </row>
     <row r="279" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A279" s="158" t="s">
-        <v>657</v>
-      </c>
+      <c r="A279" s="52"/>
       <c r="B279" s="69"/>
       <c r="C279" s="64"/>
       <c r="E279" s="35" t="s">
@@ -26032,8 +26007,8 @@
       <c r="G279" s="36">
         <v>9</v>
       </c>
-      <c r="H279" s="157">
-        <v>309</v>
+      <c r="H279" s="156">
+        <v>11.7</v>
       </c>
       <c r="I279" s="37">
         <v>41.7</v>
@@ -32685,7 +32660,7 @@
       </c>
       <c r="B463" s="70"/>
       <c r="C463" s="73"/>
-      <c r="D463" s="156" t="s">
+      <c r="D463" t="s">
         <v>655</v>
       </c>
       <c r="E463" s="52"/>
@@ -32805,7 +32780,7 @@
       </c>
       <c r="B467" s="70"/>
       <c r="C467" s="73"/>
-      <c r="D467" s="156" t="s">
+      <c r="D467" t="s">
         <v>656</v>
       </c>
       <c r="E467" s="52"/>
@@ -49883,7 +49858,7 @@
       <c r="B959" s="70"/>
       <c r="C959" s="73"/>
       <c r="D959" s="52" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E959" s="52"/>
       <c r="F959" s="52"/>
@@ -54101,7 +54076,7 @@
       </c>
       <c r="B1083" s="70"/>
       <c r="C1083" s="87" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D1083" s="52"/>
       <c r="E1083" s="52"/>
@@ -54280,7 +54255,7 @@
       <c r="B1089" s="70"/>
       <c r="C1089" s="73"/>
       <c r="D1089" s="78" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E1089" s="52"/>
       <c r="F1089" s="52"/>
@@ -70525,7 +70500,7 @@
       </c>
       <c r="B1558" s="70"/>
       <c r="C1558" s="87" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D1558" s="52"/>
       <c r="E1558" s="52"/>

--- a/Aeolus-Wireframe-06.xlsx
+++ b/Aeolus-Wireframe-06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cld\Aeolus-Tire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED13743E-E722-4932-927F-5743CAFC6D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D5249F-8DF4-4BEF-BD44-A6471EC69A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18936" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Support" sheetId="1" r:id="rId1"/>
@@ -3945,7 +3945,7 @@
     <col min="20" max="20" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="5.6640625" style="14" customWidth="1"/>
     <col min="22" max="22" width="5.21875" style="14" customWidth="1"/>
-    <col min="23" max="23" width="6.44140625" style="14" customWidth="1"/>
+    <col min="23" max="23" width="6.44140625" style="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="11.6640625" style="5" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="2.21875" customWidth="1"/>
     <col min="31" max="31" width="20.77734375" customWidth="1"/>
